--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3804,6 +3804,4468 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126057942</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>550179</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6943131</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126034784</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>550077</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6943249</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav i området</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126057387</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98355</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>550127</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6943306</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126057925</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>550203</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6943259</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126034466</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>550070</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6943181</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126057943</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>550202</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6943216</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126034754</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>550066</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6943216</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126035100</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>550152</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6943218</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126035073</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>550142</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6943223</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126034913</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>550089</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6943257</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126034773</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>550077</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6943249</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126057394</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>550077</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6943175</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126057391</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>550083</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6943127</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126057405</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>550073</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6943181</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>10 ex</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126057381</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>550076</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6943158</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre spår</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126057933</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91246</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>550185</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6943280</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126033807</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>550023</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6943027</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126057395</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>550130</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6943287</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>120 ex</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126057386</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80100</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>550139</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6943330</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126057941</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>550157</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6943042</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126033952</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>550004</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6943033</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126057392</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>550121</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6943289</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126033819</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>550004</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6943033</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126035217</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>550160</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6943218</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126057948</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>550202</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6943212</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>6 stycken</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126033968</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>550004</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6943033</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126057398</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>550112</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6943293</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126057901</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>550208</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6943249</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126034945</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>550105</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6943253</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126034055</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>550049</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6943143</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av svampen i områet</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126057400</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>550058</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6943054</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126034470</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>550080</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6943183</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126035265</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>550162</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6943239</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126035140</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>550152</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6943218</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126057383</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>550081</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6943139</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre spår</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126035020</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>550113</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6943241</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall äldre exemplar</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126057949</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>550207</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6943221</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>20stycken</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126057399</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>550041</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6943120</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126057397</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>550127</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6943295</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>80 ex</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126057404</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>550098</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6943200</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2 ex</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126057380</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>550099</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6943282</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Färskt</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126057403</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92518</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>550078</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6943240</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>11 ex</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126057389</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>550212</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6943141</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126057384</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>550026</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6943025</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4006,45 +4006,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057387</v>
+        <v>126057925</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>98334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550127</v>
+        <v>550203</v>
       </c>
       <c r="R31" t="n">
-        <v>6943306</v>
+        <v>6943259</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4077,6 +4077,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4103,45 +4108,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057925</v>
+        <v>126057387</v>
       </c>
       <c r="B32" t="n">
-        <v>98334</v>
+        <v>98355</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550203</v>
+        <v>550127</v>
       </c>
       <c r="R32" t="n">
-        <v>6943259</v>
+        <v>6943306</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4174,11 +4179,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5321,10 +5321,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057933</v>
+        <v>126033807</v>
       </c>
       <c r="B44" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5332,37 +5332,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550185</v>
+        <v>550023</v>
       </c>
       <c r="R44" t="n">
-        <v>6943280</v>
+        <v>6943027</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5392,6 +5397,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,10 +5428,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126033807</v>
+        <v>126057933</v>
       </c>
       <c r="B45" t="n">
-        <v>57651</v>
+        <v>91246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5429,42 +5439,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550023</v>
+        <v>550185</v>
       </c>
       <c r="R45" t="n">
-        <v>6943027</v>
+        <v>6943280</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5494,11 +5499,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5821,42 +5821,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126033952</v>
+        <v>126033819</v>
       </c>
       <c r="B49" t="n">
-        <v>92518</v>
+        <v>57651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5905,7 +5901,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5932,48 +5928,57 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126057392</v>
+        <v>126033952</v>
       </c>
       <c r="B50" t="n">
-        <v>80071</v>
+        <v>92518</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R50" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6003,6 +6008,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6029,10 +6039,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126033819</v>
+        <v>126057392</v>
       </c>
       <c r="B51" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6040,42 +6050,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R51" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6105,11 +6110,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6136,57 +6136,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126035217</v>
+        <v>126057398</v>
       </c>
       <c r="B52" t="n">
-        <v>92518</v>
+        <v>78968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550160</v>
+        <v>550112</v>
       </c>
       <c r="R52" t="n">
-        <v>6943218</v>
+        <v>6943293</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6220,7 +6211,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6247,10 +6238,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057948</v>
+        <v>126057901</v>
       </c>
       <c r="B53" t="n">
-        <v>92518</v>
+        <v>80099</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6258,21 +6249,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6282,10 +6273,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550202</v>
+        <v>550208</v>
       </c>
       <c r="R53" t="n">
-        <v>6943212</v>
+        <v>6943249</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6318,11 +6309,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6349,48 +6335,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126033968</v>
+        <v>126057948</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>92518</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550004</v>
+        <v>550202</v>
       </c>
       <c r="R54" t="n">
-        <v>6943033</v>
+        <v>6943212</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6420,6 +6406,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6446,7 +6437,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057398</v>
+        <v>126033968</v>
       </c>
       <c r="B55" t="n">
         <v>78968</v>
@@ -6481,13 +6472,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550112</v>
+        <v>550004</v>
       </c>
       <c r="R55" t="n">
-        <v>6943293</v>
+        <v>6943033</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6517,11 +6508,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6548,10 +6534,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057901</v>
+        <v>126035217</v>
       </c>
       <c r="B56" t="n">
-        <v>80099</v>
+        <v>92518</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6559,37 +6545,46 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550208</v>
+        <v>550160</v>
       </c>
       <c r="R56" t="n">
-        <v>6943249</v>
+        <v>6943218</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6619,6 +6614,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,7 +6645,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034945</v>
+        <v>126034055</v>
       </c>
       <c r="B57" t="n">
         <v>92518</v>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550105</v>
+        <v>550049</v>
       </c>
       <c r="R57" t="n">
-        <v>6943253</v>
+        <v>6943143</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6725,6 +6725,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6751,57 +6756,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034055</v>
+        <v>126057400</v>
       </c>
       <c r="B58" t="n">
-        <v>92518</v>
+        <v>78968</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550049</v>
+        <v>550058</v>
       </c>
       <c r="R58" t="n">
-        <v>6943143</v>
+        <v>6943054</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6831,11 +6827,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6862,48 +6853,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126057400</v>
+        <v>126034945</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>92518</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550058</v>
+        <v>550105</v>
       </c>
       <c r="R59" t="n">
-        <v>6943054</v>
+        <v>6943253</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -3810,7 +3810,7 @@
         <v>126057942</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>126034784</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4006,45 +4006,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057925</v>
+        <v>126057387</v>
       </c>
       <c r="B31" t="n">
-        <v>98334</v>
+        <v>98359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550203</v>
+        <v>550127</v>
       </c>
       <c r="R31" t="n">
-        <v>6943259</v>
+        <v>6943306</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4077,11 +4077,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4108,45 +4103,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057387</v>
+        <v>126057925</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>98338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550127</v>
+        <v>550203</v>
       </c>
       <c r="R32" t="n">
-        <v>6943306</v>
+        <v>6943259</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4179,6 +4174,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4205,10 +4205,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126034466</v>
+        <v>126057943</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4236,17 +4236,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550070</v>
+        <v>550202</v>
       </c>
       <c r="R33" t="n">
-        <v>6943181</v>
+        <v>6943216</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4276,11 +4276,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4307,10 +4302,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057943</v>
+        <v>126034466</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4338,17 +4333,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550202</v>
+        <v>550070</v>
       </c>
       <c r="R34" t="n">
-        <v>6943216</v>
+        <v>6943181</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4378,6 +4373,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4407,7 +4407,7 @@
         <v>126034754</v>
       </c>
       <c r="B35" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>126035100</v>
       </c>
       <c r="B36" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>126035073</v>
       </c>
       <c r="B37" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034913</v>
+        <v>126057394</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>78730</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550089</v>
+        <v>550077</v>
       </c>
       <c r="R38" t="n">
-        <v>6943257</v>
+        <v>6943175</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4785,11 +4785,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4816,53 +4811,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034773</v>
+        <v>126057405</v>
       </c>
       <c r="B39" t="n">
-        <v>57651</v>
+        <v>92522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550077</v>
+        <v>550073</v>
       </c>
       <c r="R39" t="n">
-        <v>6943249</v>
+        <v>6943181</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4896,7 +4886,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,10 +4913,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057394</v>
+        <v>126057391</v>
       </c>
       <c r="B40" t="n">
-        <v>78726</v>
+        <v>78731</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,21 +4924,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4958,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550077</v>
+        <v>550083</v>
       </c>
       <c r="R40" t="n">
-        <v>6943175</v>
+        <v>6943127</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5020,10 +5010,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057391</v>
+        <v>126034913</v>
       </c>
       <c r="B41" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,21 +5021,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5055,13 +5045,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550083</v>
+        <v>550089</v>
       </c>
       <c r="R41" t="n">
-        <v>6943127</v>
+        <v>6943257</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5091,6 +5081,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5117,48 +5112,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057405</v>
+        <v>126034773</v>
       </c>
       <c r="B42" t="n">
-        <v>92518</v>
+        <v>57651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550073</v>
+        <v>550077</v>
       </c>
       <c r="R42" t="n">
-        <v>6943181</v>
+        <v>6943249</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5321,10 +5321,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126033807</v>
+        <v>126057933</v>
       </c>
       <c r="B44" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5332,42 +5332,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550023</v>
+        <v>550185</v>
       </c>
       <c r="R44" t="n">
-        <v>6943027</v>
+        <v>6943280</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,11 +5392,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,10 +5418,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057933</v>
+        <v>126033807</v>
       </c>
       <c r="B45" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5439,37 +5429,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550185</v>
+        <v>550023</v>
       </c>
       <c r="R45" t="n">
-        <v>6943280</v>
+        <v>6943027</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5499,6 +5494,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5525,32 +5525,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057395</v>
+        <v>126057386</v>
       </c>
       <c r="B46" t="n">
-        <v>98334</v>
+        <v>80104</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550130</v>
+        <v>550139</v>
       </c>
       <c r="R46" t="n">
-        <v>6943287</v>
+        <v>6943330</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5596,11 +5596,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5627,45 +5622,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057386</v>
+        <v>126057941</v>
       </c>
       <c r="B47" t="n">
-        <v>80100</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550139</v>
+        <v>550157</v>
       </c>
       <c r="R47" t="n">
-        <v>6943330</v>
+        <v>6943042</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5724,45 +5719,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057941</v>
+        <v>126057395</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550157</v>
+        <v>550130</v>
       </c>
       <c r="R48" t="n">
-        <v>6943042</v>
+        <v>6943287</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5795,6 +5790,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126033819</v>
+        <v>126057392</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5832,42 +5832,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R49" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5897,11 +5892,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5931,7 +5921,7 @@
         <v>126033952</v>
       </c>
       <c r="B50" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,10 +6029,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126057392</v>
+        <v>126033819</v>
       </c>
       <c r="B51" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6050,37 +6040,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R51" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6110,6 +6105,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6136,45 +6136,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126057398</v>
+        <v>126057901</v>
       </c>
       <c r="B52" t="n">
-        <v>78968</v>
+        <v>80103</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550112</v>
+        <v>550208</v>
       </c>
       <c r="R52" t="n">
-        <v>6943293</v>
+        <v>6943249</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6207,11 +6207,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6238,45 +6233,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057901</v>
+        <v>126057398</v>
       </c>
       <c r="B53" t="n">
-        <v>80099</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550208</v>
+        <v>550112</v>
       </c>
       <c r="R53" t="n">
-        <v>6943249</v>
+        <v>6943293</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6309,6 +6304,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6338,7 +6338,7 @@
         <v>126057948</v>
       </c>
       <c r="B54" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>126033968</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>126035217</v>
       </c>
       <c r="B56" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6645,57 +6645,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034055</v>
+        <v>126057400</v>
       </c>
       <c r="B57" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550049</v>
+        <v>550058</v>
       </c>
       <c r="R57" t="n">
-        <v>6943143</v>
+        <v>6943054</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6725,11 +6716,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6756,48 +6742,57 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126057400</v>
+        <v>126034055</v>
       </c>
       <c r="B58" t="n">
-        <v>78968</v>
+        <v>92522</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550058</v>
+        <v>550049</v>
       </c>
       <c r="R58" t="n">
-        <v>6943054</v>
+        <v>6943143</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6827,6 +6822,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6856,7 +6856,7 @@
         <v>126034945</v>
       </c>
       <c r="B59" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>126034470</v>
       </c>
       <c r="B60" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126035265</v>
+        <v>126057383</v>
       </c>
       <c r="B61" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550162</v>
+        <v>550081</v>
       </c>
       <c r="R61" t="n">
-        <v>6943239</v>
+        <v>6943139</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7127,6 +7127,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7153,10 +7158,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126035140</v>
+        <v>126035265</v>
       </c>
       <c r="B62" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7164,21 +7169,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7188,10 +7193,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550152</v>
+        <v>550162</v>
       </c>
       <c r="R62" t="n">
-        <v>6943218</v>
+        <v>6943239</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7224,11 +7229,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7255,10 +7255,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057383</v>
+        <v>126035140</v>
       </c>
       <c r="B63" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550081</v>
+        <v>550152</v>
       </c>
       <c r="R63" t="n">
-        <v>6943139</v>
+        <v>6943218</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Äldre spår</t>
+          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7466,7 +7466,7 @@
         <v>126057949</v>
       </c>
       <c r="B65" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7565,32 +7565,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126057399</v>
+        <v>126057397</v>
       </c>
       <c r="B66" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550041</v>
+        <v>550127</v>
       </c>
       <c r="R66" t="n">
-        <v>6943120</v>
+        <v>6943295</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7636,6 +7636,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7662,32 +7667,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126057397</v>
+        <v>126057399</v>
       </c>
       <c r="B67" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7697,10 +7702,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550127</v>
+        <v>550041</v>
       </c>
       <c r="R67" t="n">
-        <v>6943295</v>
+        <v>6943120</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7733,11 +7738,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7764,32 +7764,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057404</v>
+        <v>126057380</v>
       </c>
       <c r="B68" t="n">
-        <v>92518</v>
+        <v>57651</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550098</v>
+        <v>550099</v>
       </c>
       <c r="R68" t="n">
-        <v>6943200</v>
+        <v>6943282</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>Ringhack på tall. Färskt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7866,32 +7866,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126057380</v>
+        <v>126057404</v>
       </c>
       <c r="B69" t="n">
-        <v>57651</v>
+        <v>92522</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550099</v>
+        <v>550098</v>
       </c>
       <c r="R69" t="n">
-        <v>6943282</v>
+        <v>6943200</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färskt</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7971,7 +7971,7 @@
         <v>126057403</v>
       </c>
       <c r="B70" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>126057389</v>
       </c>
       <c r="B71" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4205,7 +4205,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057943</v>
+        <v>126034466</v>
       </c>
       <c r="B33" t="n">
         <v>78972</v>
@@ -4236,17 +4236,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550202</v>
+        <v>550070</v>
       </c>
       <c r="R33" t="n">
-        <v>6943216</v>
+        <v>6943181</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4276,6 +4276,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,45 +4307,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126034466</v>
+        <v>126034754</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550070</v>
+        <v>550066</v>
       </c>
       <c r="R34" t="n">
-        <v>6943181</v>
+        <v>6943216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4377,7 +4391,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,10 +4418,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126034754</v>
+        <v>126035100</v>
       </c>
       <c r="B35" t="n">
-        <v>92522</v>
+        <v>80103</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,43 +4429,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550066</v>
+        <v>550152</v>
       </c>
       <c r="R35" t="n">
-        <v>6943216</v>
+        <v>6943218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4484,11 +4489,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,32 +4515,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126035100</v>
+        <v>126035073</v>
       </c>
       <c r="B36" t="n">
-        <v>80103</v>
+        <v>80075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550152</v>
+        <v>550142</v>
       </c>
       <c r="R36" t="n">
-        <v>6943218</v>
+        <v>6943223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,6 +4586,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4612,10 +4617,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126035073</v>
+        <v>126057943</v>
       </c>
       <c r="B37" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4623,37 +4628,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550142</v>
+        <v>550202</v>
       </c>
       <c r="R37" t="n">
-        <v>6943223</v>
+        <v>6943216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4683,11 +4688,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5525,32 +5525,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057386</v>
+        <v>126057395</v>
       </c>
       <c r="B46" t="n">
-        <v>80104</v>
+        <v>98338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550139</v>
+        <v>550130</v>
       </c>
       <c r="R46" t="n">
-        <v>6943330</v>
+        <v>6943287</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5596,6 +5596,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5622,45 +5627,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057941</v>
+        <v>126057386</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>80104</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550157</v>
+        <v>550139</v>
       </c>
       <c r="R47" t="n">
-        <v>6943042</v>
+        <v>6943330</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5719,45 +5724,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057395</v>
+        <v>126057941</v>
       </c>
       <c r="B48" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550130</v>
+        <v>550157</v>
       </c>
       <c r="R48" t="n">
-        <v>6943287</v>
+        <v>6943042</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5790,11 +5795,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4009,7 +4009,7 @@
         <v>126057387</v>
       </c>
       <c r="B31" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>126057925</v>
       </c>
       <c r="B32" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4205,32 +4205,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126034466</v>
+        <v>126035100</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>80103</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550070</v>
+        <v>550152</v>
       </c>
       <c r="R33" t="n">
-        <v>6943181</v>
+        <v>6943218</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,11 +4276,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4307,54 +4302,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126034754</v>
+        <v>126034466</v>
       </c>
       <c r="B34" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550066</v>
+        <v>550070</v>
       </c>
       <c r="R34" t="n">
-        <v>6943216</v>
+        <v>6943181</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4391,7 +4377,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,10 +4404,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126035100</v>
+        <v>126034754</v>
       </c>
       <c r="B35" t="n">
-        <v>80103</v>
+        <v>92522</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,34 +4415,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550152</v>
+        <v>550066</v>
       </c>
       <c r="R35" t="n">
-        <v>6943218</v>
+        <v>6943216</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4489,6 +4484,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057394</v>
+        <v>126057391</v>
       </c>
       <c r="B38" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550077</v>
+        <v>550083</v>
       </c>
       <c r="R38" t="n">
-        <v>6943175</v>
+        <v>6943127</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4811,32 +4811,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057405</v>
+        <v>126034913</v>
       </c>
       <c r="B39" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4846,13 +4846,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550073</v>
+        <v>550089</v>
       </c>
       <c r="R39" t="n">
-        <v>6943181</v>
+        <v>6943257</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4913,10 +4913,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057391</v>
+        <v>126057394</v>
       </c>
       <c r="B40" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4924,21 +4924,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550083</v>
+        <v>550077</v>
       </c>
       <c r="R40" t="n">
-        <v>6943127</v>
+        <v>6943175</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5010,32 +5010,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126034913</v>
+        <v>126057405</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550089</v>
+        <v>550073</v>
       </c>
       <c r="R41" t="n">
-        <v>6943257</v>
+        <v>6943181</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5525,45 +5525,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057395</v>
+        <v>126057941</v>
       </c>
       <c r="B46" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550130</v>
+        <v>550157</v>
       </c>
       <c r="R46" t="n">
-        <v>6943287</v>
+        <v>6943042</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5596,11 +5596,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5724,45 +5719,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057941</v>
+        <v>126057395</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550157</v>
+        <v>550130</v>
       </c>
       <c r="R48" t="n">
-        <v>6943042</v>
+        <v>6943287</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5795,6 +5790,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6136,45 +6136,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126057901</v>
+        <v>126057398</v>
       </c>
       <c r="B52" t="n">
-        <v>80103</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550208</v>
+        <v>550112</v>
       </c>
       <c r="R52" t="n">
-        <v>6943249</v>
+        <v>6943293</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6207,6 +6207,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6233,45 +6238,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057398</v>
+        <v>126057948</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550112</v>
+        <v>550202</v>
       </c>
       <c r="R53" t="n">
-        <v>6943293</v>
+        <v>6943212</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6308,7 +6313,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6335,10 +6340,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057948</v>
+        <v>126057901</v>
       </c>
       <c r="B54" t="n">
-        <v>92522</v>
+        <v>80103</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6346,21 +6351,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6370,10 +6375,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550202</v>
+        <v>550208</v>
       </c>
       <c r="R54" t="n">
-        <v>6943212</v>
+        <v>6943249</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6406,11 +6411,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057383</v>
+        <v>126035265</v>
       </c>
       <c r="B61" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550081</v>
+        <v>550162</v>
       </c>
       <c r="R61" t="n">
-        <v>6943139</v>
+        <v>6943239</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7127,11 +7127,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7158,10 +7153,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126035265</v>
+        <v>126035140</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7169,21 +7164,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7193,10 +7188,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550162</v>
+        <v>550152</v>
       </c>
       <c r="R62" t="n">
-        <v>6943239</v>
+        <v>6943218</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7229,6 +7224,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7255,10 +7255,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126035140</v>
+        <v>126057383</v>
       </c>
       <c r="B63" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550152</v>
+        <v>550081</v>
       </c>
       <c r="R63" t="n">
-        <v>6943218</v>
+        <v>6943139</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7565,32 +7565,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126057397</v>
+        <v>126057399</v>
       </c>
       <c r="B66" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550127</v>
+        <v>550041</v>
       </c>
       <c r="R66" t="n">
-        <v>6943295</v>
+        <v>6943120</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7636,11 +7636,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7667,32 +7662,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126057399</v>
+        <v>126057397</v>
       </c>
       <c r="B67" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7702,10 +7697,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550041</v>
+        <v>550127</v>
       </c>
       <c r="R67" t="n">
-        <v>6943120</v>
+        <v>6943295</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7738,6 +7733,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7764,32 +7764,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057380</v>
+        <v>126057404</v>
       </c>
       <c r="B68" t="n">
-        <v>57651</v>
+        <v>92522</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550099</v>
+        <v>550098</v>
       </c>
       <c r="R68" t="n">
-        <v>6943282</v>
+        <v>6943200</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färskt</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7866,7 +7866,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126057404</v>
+        <v>126057403</v>
       </c>
       <c r="B69" t="n">
         <v>92522</v>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550098</v>
+        <v>550078</v>
       </c>
       <c r="R69" t="n">
-        <v>6943200</v>
+        <v>6943240</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7968,32 +7968,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057403</v>
+        <v>126057380</v>
       </c>
       <c r="B70" t="n">
-        <v>92522</v>
+        <v>57651</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550078</v>
+        <v>550099</v>
       </c>
       <c r="R70" t="n">
-        <v>6943240</v>
+        <v>6943282</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Ringhack på tall. Färskt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8070,10 +8070,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126057389</v>
+        <v>126057384</v>
       </c>
       <c r="B71" t="n">
-        <v>78731</v>
+        <v>57651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8081,21 +8081,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550212</v>
+        <v>550026</v>
       </c>
       <c r="R71" t="n">
-        <v>6943141</v>
+        <v>6943025</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8141,6 +8141,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8167,10 +8172,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126057384</v>
+        <v>126057389</v>
       </c>
       <c r="B72" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8178,21 +8183,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8202,10 +8207,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550026</v>
+        <v>550212</v>
       </c>
       <c r="R72" t="n">
-        <v>6943025</v>
+        <v>6943141</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8238,11 +8243,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4205,32 +4205,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126035100</v>
+        <v>126034466</v>
       </c>
       <c r="B33" t="n">
-        <v>80103</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550152</v>
+        <v>550070</v>
       </c>
       <c r="R33" t="n">
-        <v>6943218</v>
+        <v>6943181</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,6 +4276,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,45 +4307,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126034466</v>
+        <v>126034754</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550070</v>
+        <v>550066</v>
       </c>
       <c r="R34" t="n">
-        <v>6943181</v>
+        <v>6943216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4377,7 +4391,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,10 +4418,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126034754</v>
+        <v>126035100</v>
       </c>
       <c r="B35" t="n">
-        <v>92522</v>
+        <v>80103</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,43 +4429,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550066</v>
+        <v>550152</v>
       </c>
       <c r="R35" t="n">
-        <v>6943216</v>
+        <v>6943218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4484,11 +4489,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5821,48 +5821,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126057392</v>
+        <v>126033952</v>
       </c>
       <c r="B49" t="n">
-        <v>80075</v>
+        <v>92522</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R49" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5892,6 +5901,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5918,57 +5932,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126033952</v>
+        <v>126057392</v>
       </c>
       <c r="B50" t="n">
-        <v>92522</v>
+        <v>80075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R50" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5998,11 +6003,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6437,45 +6437,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126033968</v>
+        <v>126035217</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550004</v>
+        <v>550160</v>
       </c>
       <c r="R55" t="n">
-        <v>6943033</v>
+        <v>6943218</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,6 +6517,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6534,54 +6548,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126035217</v>
+        <v>126033968</v>
       </c>
       <c r="B56" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550160</v>
+        <v>550004</v>
       </c>
       <c r="R56" t="n">
-        <v>6943218</v>
+        <v>6943033</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6614,11 +6619,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126035265</v>
+        <v>126057383</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550162</v>
+        <v>550081</v>
       </c>
       <c r="R61" t="n">
-        <v>6943239</v>
+        <v>6943139</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7127,6 +7127,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7153,10 +7158,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126035140</v>
+        <v>126035265</v>
       </c>
       <c r="B62" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7164,21 +7169,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7188,10 +7193,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550152</v>
+        <v>550162</v>
       </c>
       <c r="R62" t="n">
-        <v>6943218</v>
+        <v>6943239</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7224,11 +7229,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7255,10 +7255,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057383</v>
+        <v>126035140</v>
       </c>
       <c r="B63" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550081</v>
+        <v>550152</v>
       </c>
       <c r="R63" t="n">
-        <v>6943139</v>
+        <v>6943218</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Äldre spår</t>
+          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -5821,57 +5821,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126033952</v>
+        <v>126057392</v>
       </c>
       <c r="B49" t="n">
-        <v>92522</v>
+        <v>80075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R49" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5901,11 +5892,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5932,48 +5918,57 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126057392</v>
+        <v>126033952</v>
       </c>
       <c r="B50" t="n">
-        <v>80075</v>
+        <v>92522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R50" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6003,6 +5998,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6437,54 +6437,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126035217</v>
+        <v>126033968</v>
       </c>
       <c r="B55" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550160</v>
+        <v>550004</v>
       </c>
       <c r="R55" t="n">
-        <v>6943218</v>
+        <v>6943033</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6517,11 +6508,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6548,45 +6534,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126033968</v>
+        <v>126035217</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550004</v>
+        <v>550160</v>
       </c>
       <c r="R56" t="n">
-        <v>6943033</v>
+        <v>6943218</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6619,6 +6614,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -3807,10 +3807,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057942</v>
+        <v>126034784</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,17 +3838,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550179</v>
+        <v>550077</v>
       </c>
       <c r="R29" t="n">
-        <v>6943131</v>
+        <v>6943249</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3878,6 +3878,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav i området</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3904,10 +3909,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126034784</v>
+        <v>126057942</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,17 +3940,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550077</v>
+        <v>550179</v>
       </c>
       <c r="R30" t="n">
-        <v>6943249</v>
+        <v>6943131</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3975,11 +3980,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav i området</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4006,45 +4006,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057387</v>
+        <v>126057925</v>
       </c>
       <c r="B31" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550127</v>
+        <v>550203</v>
       </c>
       <c r="R31" t="n">
-        <v>6943306</v>
+        <v>6943259</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4077,6 +4077,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4103,45 +4108,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057925</v>
+        <v>126057387</v>
       </c>
       <c r="B32" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550203</v>
+        <v>550127</v>
       </c>
       <c r="R32" t="n">
-        <v>6943259</v>
+        <v>6943306</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4174,11 +4179,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4205,32 +4205,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126034466</v>
+        <v>126035100</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>80104</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550070</v>
+        <v>550152</v>
       </c>
       <c r="R33" t="n">
-        <v>6943181</v>
+        <v>6943218</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,11 +4276,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4307,54 +4302,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126034754</v>
+        <v>126034466</v>
       </c>
       <c r="B34" t="n">
-        <v>92522</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550066</v>
+        <v>550070</v>
       </c>
       <c r="R34" t="n">
-        <v>6943216</v>
+        <v>6943181</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4391,7 +4377,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,10 +4404,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126035100</v>
+        <v>126034754</v>
       </c>
       <c r="B35" t="n">
-        <v>80103</v>
+        <v>92524</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,34 +4415,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550152</v>
+        <v>550066</v>
       </c>
       <c r="R35" t="n">
-        <v>6943218</v>
+        <v>6943216</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4489,6 +4484,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,7 +4518,7 @@
         <v>126035073</v>
       </c>
       <c r="B36" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>126057943</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057391</v>
+        <v>126034773</v>
       </c>
       <c r="B38" t="n">
-        <v>78731</v>
+        <v>57652</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,37 +4725,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550083</v>
+        <v>550077</v>
       </c>
       <c r="R38" t="n">
-        <v>6943127</v>
+        <v>6943249</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4785,6 +4790,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4814,7 +4824,7 @@
         <v>126034913</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4913,10 +4923,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057394</v>
+        <v>126057391</v>
       </c>
       <c r="B40" t="n">
-        <v>78730</v>
+        <v>78732</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4924,21 +4934,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4948,10 +4958,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550077</v>
+        <v>550083</v>
       </c>
       <c r="R40" t="n">
-        <v>6943175</v>
+        <v>6943127</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5010,32 +5020,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057405</v>
+        <v>126057394</v>
       </c>
       <c r="B41" t="n">
-        <v>92522</v>
+        <v>78731</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5045,10 +5055,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550073</v>
+        <v>550077</v>
       </c>
       <c r="R41" t="n">
-        <v>6943181</v>
+        <v>6943175</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5081,11 +5091,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5112,53 +5117,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126034773</v>
+        <v>126057405</v>
       </c>
       <c r="B42" t="n">
-        <v>57651</v>
+        <v>92524</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550077</v>
+        <v>550073</v>
       </c>
       <c r="R42" t="n">
-        <v>6943249</v>
+        <v>6943181</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,7 +5222,7 @@
         <v>126057381</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057933</v>
+        <v>126033807</v>
       </c>
       <c r="B44" t="n">
-        <v>91250</v>
+        <v>57652</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5332,37 +5332,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550185</v>
+        <v>550023</v>
       </c>
       <c r="R44" t="n">
-        <v>6943280</v>
+        <v>6943027</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5392,6 +5397,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,10 +5428,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126033807</v>
+        <v>126057933</v>
       </c>
       <c r="B45" t="n">
-        <v>57651</v>
+        <v>91252</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5429,42 +5439,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550023</v>
+        <v>550185</v>
       </c>
       <c r="R45" t="n">
-        <v>6943027</v>
+        <v>6943280</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5494,11 +5499,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5525,45 +5525,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057941</v>
+        <v>126057395</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550157</v>
+        <v>550130</v>
       </c>
       <c r="R46" t="n">
-        <v>6943042</v>
+        <v>6943287</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5596,6 +5596,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5622,45 +5627,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057386</v>
+        <v>126057941</v>
       </c>
       <c r="B47" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550139</v>
+        <v>550157</v>
       </c>
       <c r="R47" t="n">
-        <v>6943330</v>
+        <v>6943042</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5719,32 +5724,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057395</v>
+        <v>126057386</v>
       </c>
       <c r="B48" t="n">
-        <v>98339</v>
+        <v>80105</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5754,10 +5759,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550130</v>
+        <v>550139</v>
       </c>
       <c r="R48" t="n">
-        <v>6943287</v>
+        <v>6943330</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5790,11 +5795,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126057392</v>
+        <v>126033819</v>
       </c>
       <c r="B49" t="n">
-        <v>80075</v>
+        <v>57652</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5832,37 +5832,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R49" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5892,6 +5897,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5921,7 +5931,7 @@
         <v>126033952</v>
       </c>
       <c r="B50" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6029,10 +6039,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126033819</v>
+        <v>126057392</v>
       </c>
       <c r="B51" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6040,42 +6050,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R51" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6105,11 +6110,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126057398</v>
+        <v>126033968</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550112</v>
+        <v>550004</v>
       </c>
       <c r="R52" t="n">
-        <v>6943293</v>
+        <v>6943033</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6207,11 +6207,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6238,10 +6233,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057948</v>
+        <v>126035217</v>
       </c>
       <c r="B53" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6266,20 +6261,29 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550202</v>
+        <v>550160</v>
       </c>
       <c r="R53" t="n">
-        <v>6943212</v>
+        <v>6943218</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6313,7 +6317,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>6 stycken</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6340,45 +6344,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057901</v>
+        <v>126057398</v>
       </c>
       <c r="B54" t="n">
-        <v>80103</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550208</v>
+        <v>550112</v>
       </c>
       <c r="R54" t="n">
-        <v>6943249</v>
+        <v>6943293</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6411,6 +6415,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6437,48 +6446,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126033968</v>
+        <v>126057948</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>92524</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550004</v>
+        <v>550202</v>
       </c>
       <c r="R55" t="n">
-        <v>6943033</v>
+        <v>6943212</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6508,6 +6517,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6534,10 +6548,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126035217</v>
+        <v>126057901</v>
       </c>
       <c r="B56" t="n">
-        <v>92522</v>
+        <v>80104</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6545,46 +6559,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550160</v>
+        <v>550208</v>
       </c>
       <c r="R56" t="n">
-        <v>6943218</v>
+        <v>6943249</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6614,11 +6619,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,48 +6645,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126057400</v>
+        <v>126034055</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>92524</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550058</v>
+        <v>550049</v>
       </c>
       <c r="R57" t="n">
-        <v>6943054</v>
+        <v>6943143</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6716,6 +6725,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6742,10 +6756,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034055</v>
+        <v>126034945</v>
       </c>
       <c r="B58" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6786,10 +6800,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550049</v>
+        <v>550105</v>
       </c>
       <c r="R58" t="n">
-        <v>6943143</v>
+        <v>6943253</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6822,11 +6836,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6853,57 +6862,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126034945</v>
+        <v>126057400</v>
       </c>
       <c r="B59" t="n">
-        <v>92522</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550105</v>
+        <v>550058</v>
       </c>
       <c r="R59" t="n">
-        <v>6943253</v>
+        <v>6943054</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>126034470</v>
       </c>
       <c r="B60" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>126057383</v>
       </c>
       <c r="B61" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>126035265</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>126035140</v>
       </c>
       <c r="B63" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>126035020</v>
       </c>
       <c r="B64" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>126057949</v>
       </c>
       <c r="B65" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>126057399</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>126057397</v>
       </c>
       <c r="B67" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7764,32 +7764,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057404</v>
+        <v>126057380</v>
       </c>
       <c r="B68" t="n">
-        <v>92522</v>
+        <v>57652</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550098</v>
+        <v>550099</v>
       </c>
       <c r="R68" t="n">
-        <v>6943200</v>
+        <v>6943282</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>Ringhack på tall. Färskt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7866,10 +7866,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126057403</v>
+        <v>126057404</v>
       </c>
       <c r="B69" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550078</v>
+        <v>550098</v>
       </c>
       <c r="R69" t="n">
-        <v>6943240</v>
+        <v>6943200</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7968,32 +7968,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057380</v>
+        <v>126057403</v>
       </c>
       <c r="B70" t="n">
-        <v>57651</v>
+        <v>92524</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550099</v>
+        <v>550078</v>
       </c>
       <c r="R70" t="n">
-        <v>6943282</v>
+        <v>6943240</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färskt</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8073,7 +8073,7 @@
         <v>126057384</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>126057389</v>
       </c>
       <c r="B72" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4006,45 +4006,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057925</v>
+        <v>126057387</v>
       </c>
       <c r="B31" t="n">
-        <v>98341</v>
+        <v>98362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550203</v>
+        <v>550127</v>
       </c>
       <c r="R31" t="n">
-        <v>6943259</v>
+        <v>6943306</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4077,11 +4077,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4108,45 +4103,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057387</v>
+        <v>126057925</v>
       </c>
       <c r="B32" t="n">
-        <v>98362</v>
+        <v>98341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550127</v>
+        <v>550203</v>
       </c>
       <c r="R32" t="n">
-        <v>6943306</v>
+        <v>6943259</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4179,6 +4174,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5321,10 +5321,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126033807</v>
+        <v>126057933</v>
       </c>
       <c r="B44" t="n">
-        <v>57652</v>
+        <v>91252</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5332,42 +5332,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550023</v>
+        <v>550185</v>
       </c>
       <c r="R44" t="n">
-        <v>6943027</v>
+        <v>6943280</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,11 +5392,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,10 +5418,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057933</v>
+        <v>126033807</v>
       </c>
       <c r="B45" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5439,37 +5429,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550185</v>
+        <v>550023</v>
       </c>
       <c r="R45" t="n">
-        <v>6943280</v>
+        <v>6943027</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5499,6 +5494,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057383</v>
+        <v>126035265</v>
       </c>
       <c r="B61" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550081</v>
+        <v>550162</v>
       </c>
       <c r="R61" t="n">
-        <v>6943139</v>
+        <v>6943239</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7127,11 +7127,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7158,10 +7153,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126035265</v>
+        <v>126035140</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7169,21 +7164,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7193,10 +7188,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550162</v>
+        <v>550152</v>
       </c>
       <c r="R62" t="n">
-        <v>6943239</v>
+        <v>6943218</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7229,6 +7224,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7255,10 +7255,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126035140</v>
+        <v>126057383</v>
       </c>
       <c r="B63" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550152</v>
+        <v>550081</v>
       </c>
       <c r="R63" t="n">
-        <v>6943218</v>
+        <v>6943139</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -3807,7 +3807,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126034784</v>
+        <v>126057942</v>
       </c>
       <c r="B29" t="n">
         <v>78973</v>
@@ -3838,17 +3838,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550077</v>
+        <v>550179</v>
       </c>
       <c r="R29" t="n">
-        <v>6943249</v>
+        <v>6943131</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3878,11 +3878,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav i området</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3909,7 +3904,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057942</v>
+        <v>126034784</v>
       </c>
       <c r="B30" t="n">
         <v>78973</v>
@@ -3940,17 +3935,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550179</v>
+        <v>550077</v>
       </c>
       <c r="R30" t="n">
-        <v>6943131</v>
+        <v>6943249</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3980,6 +3975,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav i området</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4009,7 +4009,7 @@
         <v>126057387</v>
       </c>
       <c r="B31" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>126057925</v>
       </c>
       <c r="B32" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4205,32 +4205,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126035100</v>
+        <v>126035073</v>
       </c>
       <c r="B33" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550152</v>
+        <v>550142</v>
       </c>
       <c r="R33" t="n">
-        <v>6943218</v>
+        <v>6943223</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,6 +4276,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,7 +4307,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126034466</v>
+        <v>126057943</v>
       </c>
       <c r="B34" t="n">
         <v>78973</v>
@@ -4333,17 +4338,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550070</v>
+        <v>550202</v>
       </c>
       <c r="R34" t="n">
-        <v>6943181</v>
+        <v>6943216</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4373,11 +4378,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,54 +4404,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126034754</v>
+        <v>126034466</v>
       </c>
       <c r="B35" t="n">
-        <v>92524</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550066</v>
+        <v>550070</v>
       </c>
       <c r="R35" t="n">
-        <v>6943216</v>
+        <v>6943181</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,7 +4479,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,45 +4506,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126035073</v>
+        <v>126034754</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>92526</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550142</v>
+        <v>550066</v>
       </c>
       <c r="R36" t="n">
-        <v>6943223</v>
+        <v>6943216</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,48 +4617,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057943</v>
+        <v>126035100</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>80104</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550202</v>
+        <v>550152</v>
       </c>
       <c r="R37" t="n">
-        <v>6943216</v>
+        <v>6943218</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034773</v>
+        <v>126057394</v>
       </c>
       <c r="B38" t="n">
-        <v>57652</v>
+        <v>78731</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,29 +4725,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
@@ -4757,10 +4752,10 @@
         <v>550077</v>
       </c>
       <c r="R38" t="n">
-        <v>6943249</v>
+        <v>6943175</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4790,11 +4785,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4821,32 +4811,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034913</v>
+        <v>126057405</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4856,13 +4846,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550089</v>
+        <v>550073</v>
       </c>
       <c r="R39" t="n">
-        <v>6943257</v>
+        <v>6943181</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4896,7 +4886,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,10 +4913,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057391</v>
+        <v>126034913</v>
       </c>
       <c r="B40" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,21 +4924,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4958,13 +4948,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550083</v>
+        <v>550089</v>
       </c>
       <c r="R40" t="n">
-        <v>6943127</v>
+        <v>6943257</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4994,6 +4984,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5020,10 +5015,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057394</v>
+        <v>126034773</v>
       </c>
       <c r="B41" t="n">
-        <v>78731</v>
+        <v>57652</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,24 +5026,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
@@ -5058,10 +5058,10 @@
         <v>550077</v>
       </c>
       <c r="R41" t="n">
-        <v>6943175</v>
+        <v>6943249</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5091,6 +5091,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5117,32 +5122,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057405</v>
+        <v>126057391</v>
       </c>
       <c r="B42" t="n">
-        <v>92524</v>
+        <v>78732</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550073</v>
+        <v>550083</v>
       </c>
       <c r="R42" t="n">
-        <v>6943181</v>
+        <v>6943127</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5188,11 +5193,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5321,10 +5321,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057933</v>
+        <v>126033807</v>
       </c>
       <c r="B44" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5332,37 +5332,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550185</v>
+        <v>550023</v>
       </c>
       <c r="R44" t="n">
-        <v>6943280</v>
+        <v>6943027</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5392,6 +5397,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,10 +5428,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126033807</v>
+        <v>126057933</v>
       </c>
       <c r="B45" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5429,42 +5439,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550023</v>
+        <v>550185</v>
       </c>
       <c r="R45" t="n">
-        <v>6943027</v>
+        <v>6943280</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5494,11 +5499,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5525,32 +5525,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057395</v>
+        <v>126057386</v>
       </c>
       <c r="B46" t="n">
-        <v>98341</v>
+        <v>80105</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550130</v>
+        <v>550139</v>
       </c>
       <c r="R46" t="n">
-        <v>6943287</v>
+        <v>6943330</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5596,11 +5596,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5724,32 +5719,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057386</v>
+        <v>126057395</v>
       </c>
       <c r="B48" t="n">
-        <v>80105</v>
+        <v>98343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5759,10 +5754,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550139</v>
+        <v>550130</v>
       </c>
       <c r="R48" t="n">
-        <v>6943330</v>
+        <v>6943287</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5795,6 +5790,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126033819</v>
+        <v>126057392</v>
       </c>
       <c r="B49" t="n">
-        <v>57652</v>
+        <v>80076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5832,42 +5832,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R49" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5897,11 +5892,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5931,7 +5921,7 @@
         <v>126033952</v>
       </c>
       <c r="B50" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,10 +6029,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126057392</v>
+        <v>126033819</v>
       </c>
       <c r="B51" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6050,37 +6040,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R51" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6110,6 +6105,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6136,48 +6136,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126033968</v>
+        <v>126057901</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>80104</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550004</v>
+        <v>550208</v>
       </c>
       <c r="R52" t="n">
-        <v>6943033</v>
+        <v>6943249</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126035217</v>
+        <v>126057948</v>
       </c>
       <c r="B53" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6261,29 +6261,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550160</v>
+        <v>550202</v>
       </c>
       <c r="R53" t="n">
-        <v>6943218</v>
+        <v>6943212</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6317,7 +6308,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6344,48 +6335,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057398</v>
+        <v>126035217</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550112</v>
+        <v>550160</v>
       </c>
       <c r="R54" t="n">
-        <v>6943293</v>
+        <v>6943218</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6446,45 +6446,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057948</v>
+        <v>126057398</v>
       </c>
       <c r="B55" t="n">
-        <v>92524</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550202</v>
+        <v>550112</v>
       </c>
       <c r="R55" t="n">
-        <v>6943212</v>
+        <v>6943293</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>6 stycken</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6548,48 +6548,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057901</v>
+        <v>126033968</v>
       </c>
       <c r="B56" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550208</v>
+        <v>550004</v>
       </c>
       <c r="R56" t="n">
-        <v>6943249</v>
+        <v>6943033</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6645,57 +6645,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034055</v>
+        <v>126057400</v>
       </c>
       <c r="B57" t="n">
-        <v>92524</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550049</v>
+        <v>550058</v>
       </c>
       <c r="R57" t="n">
-        <v>6943143</v>
+        <v>6943054</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6725,11 +6716,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6756,10 +6742,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034945</v>
+        <v>126034055</v>
       </c>
       <c r="B58" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6800,10 +6786,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550105</v>
+        <v>550049</v>
       </c>
       <c r="R58" t="n">
-        <v>6943253</v>
+        <v>6943143</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6836,6 +6822,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6862,48 +6853,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126057400</v>
+        <v>126034945</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550058</v>
+        <v>550105</v>
       </c>
       <c r="R59" t="n">
-        <v>6943054</v>
+        <v>6943253</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126035265</v>
+        <v>126057383</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550162</v>
+        <v>550081</v>
       </c>
       <c r="R61" t="n">
-        <v>6943239</v>
+        <v>6943139</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7127,6 +7127,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7255,10 +7260,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057383</v>
+        <v>126035265</v>
       </c>
       <c r="B63" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7266,21 +7271,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7290,13 +7295,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550081</v>
+        <v>550162</v>
       </c>
       <c r="R63" t="n">
-        <v>6943139</v>
+        <v>6943239</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7326,11 +7331,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7466,7 +7466,7 @@
         <v>126057949</v>
       </c>
       <c r="B65" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>126057397</v>
       </c>
       <c r="B67" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>126057404</v>
       </c>
       <c r="B69" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>126057403</v>
       </c>
       <c r="B70" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -5321,10 +5321,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126033807</v>
+        <v>126057933</v>
       </c>
       <c r="B44" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5332,42 +5332,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550023</v>
+        <v>550185</v>
       </c>
       <c r="R44" t="n">
-        <v>6943027</v>
+        <v>6943280</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,11 +5392,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,10 +5418,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057933</v>
+        <v>126033807</v>
       </c>
       <c r="B45" t="n">
-        <v>91254</v>
+        <v>57652</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5439,37 +5429,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550185</v>
+        <v>550023</v>
       </c>
       <c r="R45" t="n">
-        <v>6943280</v>
+        <v>6943027</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5499,6 +5494,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5525,32 +5525,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057386</v>
+        <v>126057395</v>
       </c>
       <c r="B46" t="n">
-        <v>80105</v>
+        <v>98343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550139</v>
+        <v>550130</v>
       </c>
       <c r="R46" t="n">
-        <v>6943330</v>
+        <v>6943287</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5596,6 +5596,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5622,45 +5627,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057941</v>
+        <v>126057386</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550157</v>
+        <v>550139</v>
       </c>
       <c r="R47" t="n">
-        <v>6943042</v>
+        <v>6943330</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5719,45 +5724,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057395</v>
+        <v>126057941</v>
       </c>
       <c r="B48" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550130</v>
+        <v>550157</v>
       </c>
       <c r="R48" t="n">
-        <v>6943287</v>
+        <v>6943042</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5790,11 +5795,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6233,48 +6233,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057948</v>
+        <v>126033968</v>
       </c>
       <c r="B53" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550202</v>
+        <v>550004</v>
       </c>
       <c r="R53" t="n">
-        <v>6943212</v>
+        <v>6943033</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6304,11 +6304,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6335,57 +6330,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126035217</v>
+        <v>126057398</v>
       </c>
       <c r="B54" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550160</v>
+        <v>550112</v>
       </c>
       <c r="R54" t="n">
-        <v>6943218</v>
+        <v>6943293</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6419,7 +6405,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6446,45 +6432,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057398</v>
+        <v>126057948</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550112</v>
+        <v>550202</v>
       </c>
       <c r="R55" t="n">
-        <v>6943293</v>
+        <v>6943212</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6521,7 +6507,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6548,45 +6534,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126033968</v>
+        <v>126035217</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550004</v>
+        <v>550160</v>
       </c>
       <c r="R56" t="n">
-        <v>6943033</v>
+        <v>6943218</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6619,6 +6614,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7764,32 +7764,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057380</v>
+        <v>126057404</v>
       </c>
       <c r="B68" t="n">
-        <v>57652</v>
+        <v>92526</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550099</v>
+        <v>550098</v>
       </c>
       <c r="R68" t="n">
-        <v>6943282</v>
+        <v>6943200</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färskt</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7866,7 +7866,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126057404</v>
+        <v>126057403</v>
       </c>
       <c r="B69" t="n">
         <v>92526</v>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550098</v>
+        <v>550078</v>
       </c>
       <c r="R69" t="n">
-        <v>6943200</v>
+        <v>6943240</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7968,32 +7968,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057403</v>
+        <v>126057380</v>
       </c>
       <c r="B70" t="n">
-        <v>92526</v>
+        <v>57652</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550078</v>
+        <v>550099</v>
       </c>
       <c r="R70" t="n">
-        <v>6943240</v>
+        <v>6943282</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Ringhack på tall. Färskt</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4006,45 +4006,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057387</v>
+        <v>126057925</v>
       </c>
       <c r="B31" t="n">
-        <v>98364</v>
+        <v>98345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550127</v>
+        <v>550203</v>
       </c>
       <c r="R31" t="n">
-        <v>6943306</v>
+        <v>6943259</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4077,6 +4077,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4103,45 +4108,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057925</v>
+        <v>126057387</v>
       </c>
       <c r="B32" t="n">
-        <v>98343</v>
+        <v>98366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550203</v>
+        <v>550127</v>
       </c>
       <c r="R32" t="n">
-        <v>6943259</v>
+        <v>6943306</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4174,11 +4179,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4205,10 +4205,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126035073</v>
+        <v>126034466</v>
       </c>
       <c r="B33" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4216,21 +4216,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550142</v>
+        <v>550070</v>
       </c>
       <c r="R33" t="n">
-        <v>6943223</v>
+        <v>6943181</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4307,48 +4307,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057943</v>
+        <v>126034754</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550202</v>
+        <v>550066</v>
       </c>
       <c r="R34" t="n">
         <v>6943216</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4378,6 +4387,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,32 +4418,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126034466</v>
+        <v>126035100</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>80104</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4439,10 +4453,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550070</v>
+        <v>550152</v>
       </c>
       <c r="R35" t="n">
-        <v>6943181</v>
+        <v>6943218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,11 +4489,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4506,54 +4515,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034754</v>
+        <v>126035073</v>
       </c>
       <c r="B36" t="n">
-        <v>92526</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550066</v>
+        <v>550142</v>
       </c>
       <c r="R36" t="n">
-        <v>6943216</v>
+        <v>6943223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,48 +4617,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126035100</v>
+        <v>126057943</v>
       </c>
       <c r="B37" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550152</v>
+        <v>550202</v>
       </c>
       <c r="R37" t="n">
-        <v>6943218</v>
+        <v>6943216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057394</v>
+        <v>126034913</v>
       </c>
       <c r="B38" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550077</v>
+        <v>550089</v>
       </c>
       <c r="R38" t="n">
-        <v>6943175</v>
+        <v>6943257</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4785,6 +4785,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4811,48 +4816,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057405</v>
+        <v>126034773</v>
       </c>
       <c r="B39" t="n">
-        <v>92526</v>
+        <v>57652</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550073</v>
+        <v>550077</v>
       </c>
       <c r="R39" t="n">
-        <v>6943181</v>
+        <v>6943249</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4886,7 +4896,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4913,10 +4923,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126034913</v>
+        <v>126057394</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4924,21 +4934,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4948,13 +4958,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550089</v>
+        <v>550077</v>
       </c>
       <c r="R40" t="n">
-        <v>6943257</v>
+        <v>6943175</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4984,11 +4994,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5015,53 +5020,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126034773</v>
+        <v>126057405</v>
       </c>
       <c r="B41" t="n">
-        <v>57652</v>
+        <v>92528</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550077</v>
+        <v>550073</v>
       </c>
       <c r="R41" t="n">
-        <v>6943249</v>
+        <v>6943181</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5324,7 +5324,7 @@
         <v>126057933</v>
       </c>
       <c r="B44" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5525,32 +5525,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057395</v>
+        <v>126057386</v>
       </c>
       <c r="B46" t="n">
-        <v>98343</v>
+        <v>80105</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550130</v>
+        <v>550139</v>
       </c>
       <c r="R46" t="n">
-        <v>6943287</v>
+        <v>6943330</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5596,11 +5596,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5627,45 +5622,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057386</v>
+        <v>126057941</v>
       </c>
       <c r="B47" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550139</v>
+        <v>550157</v>
       </c>
       <c r="R47" t="n">
-        <v>6943330</v>
+        <v>6943042</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5724,45 +5719,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057941</v>
+        <v>126057395</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550157</v>
+        <v>550130</v>
       </c>
       <c r="R48" t="n">
-        <v>6943042</v>
+        <v>6943287</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5795,6 +5790,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5918,42 +5918,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126033952</v>
+        <v>126033819</v>
       </c>
       <c r="B50" t="n">
-        <v>92526</v>
+        <v>57652</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6002,7 +5998,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6029,38 +6025,42 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126033819</v>
+        <v>126033952</v>
       </c>
       <c r="B51" t="n">
-        <v>57652</v>
+        <v>92528</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6136,48 +6136,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126057901</v>
+        <v>126033968</v>
       </c>
       <c r="B52" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550208</v>
+        <v>550004</v>
       </c>
       <c r="R52" t="n">
-        <v>6943249</v>
+        <v>6943033</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6233,45 +6233,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126033968</v>
+        <v>126035217</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550004</v>
+        <v>550160</v>
       </c>
       <c r="R53" t="n">
-        <v>6943033</v>
+        <v>6943218</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,6 +6313,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6330,45 +6344,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057398</v>
+        <v>126057901</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>80104</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550112</v>
+        <v>550208</v>
       </c>
       <c r="R54" t="n">
-        <v>6943293</v>
+        <v>6943249</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6401,11 +6415,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6432,45 +6441,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057948</v>
+        <v>126057398</v>
       </c>
       <c r="B55" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550202</v>
+        <v>550112</v>
       </c>
       <c r="R55" t="n">
-        <v>6943212</v>
+        <v>6943293</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6507,7 +6516,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>6 stycken</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6534,10 +6543,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126035217</v>
+        <v>126057948</v>
       </c>
       <c r="B56" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6562,29 +6571,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550160</v>
+        <v>550202</v>
       </c>
       <c r="R56" t="n">
-        <v>6943218</v>
+        <v>6943212</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,48 +6645,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126057400</v>
+        <v>126034055</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550058</v>
+        <v>550049</v>
       </c>
       <c r="R57" t="n">
-        <v>6943054</v>
+        <v>6943143</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6716,6 +6725,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6742,10 +6756,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034055</v>
+        <v>126034945</v>
       </c>
       <c r="B58" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6786,10 +6800,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550049</v>
+        <v>550105</v>
       </c>
       <c r="R58" t="n">
-        <v>6943143</v>
+        <v>6943253</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6822,11 +6836,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6853,57 +6862,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126034945</v>
+        <v>126057400</v>
       </c>
       <c r="B59" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550105</v>
+        <v>550058</v>
       </c>
       <c r="R59" t="n">
-        <v>6943253</v>
+        <v>6943054</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057383</v>
+        <v>126035265</v>
       </c>
       <c r="B61" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550081</v>
+        <v>550162</v>
       </c>
       <c r="R61" t="n">
-        <v>6943139</v>
+        <v>6943239</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7127,11 +7127,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7260,10 +7255,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126035265</v>
+        <v>126057383</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7271,21 +7266,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7295,13 +7290,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550162</v>
+        <v>550081</v>
       </c>
       <c r="R63" t="n">
-        <v>6943239</v>
+        <v>6943139</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7331,6 +7326,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7466,7 +7466,7 @@
         <v>126057949</v>
       </c>
       <c r="B65" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>126057397</v>
       </c>
       <c r="B67" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7764,32 +7764,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057404</v>
+        <v>126057380</v>
       </c>
       <c r="B68" t="n">
-        <v>92526</v>
+        <v>57652</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550098</v>
+        <v>550099</v>
       </c>
       <c r="R68" t="n">
-        <v>6943200</v>
+        <v>6943282</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>Ringhack på tall. Färskt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7866,10 +7866,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126057403</v>
+        <v>126057404</v>
       </c>
       <c r="B69" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550078</v>
+        <v>550098</v>
       </c>
       <c r="R69" t="n">
-        <v>6943240</v>
+        <v>6943200</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7968,32 +7968,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057380</v>
+        <v>126057403</v>
       </c>
       <c r="B70" t="n">
-        <v>57652</v>
+        <v>92528</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550099</v>
+        <v>550078</v>
       </c>
       <c r="R70" t="n">
-        <v>6943282</v>
+        <v>6943240</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färskt</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -5821,10 +5821,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126057392</v>
+        <v>126033819</v>
       </c>
       <c r="B49" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5832,37 +5832,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R49" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5892,6 +5897,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5918,38 +5928,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126033819</v>
+        <v>126033952</v>
       </c>
       <c r="B50" t="n">
-        <v>57652</v>
+        <v>92528</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5998,7 +6012,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6025,57 +6039,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126033952</v>
+        <v>126057392</v>
       </c>
       <c r="B51" t="n">
-        <v>92528</v>
+        <v>80076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R51" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6105,11 +6110,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6233,10 +6233,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126035217</v>
+        <v>126057901</v>
       </c>
       <c r="B53" t="n">
-        <v>92528</v>
+        <v>80104</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6244,46 +6244,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550160</v>
+        <v>550208</v>
       </c>
       <c r="R53" t="n">
-        <v>6943218</v>
+        <v>6943249</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6313,11 +6304,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6344,45 +6330,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057901</v>
+        <v>126057398</v>
       </c>
       <c r="B54" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550208</v>
+        <v>550112</v>
       </c>
       <c r="R54" t="n">
-        <v>6943249</v>
+        <v>6943293</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6415,6 +6401,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6441,45 +6432,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057398</v>
+        <v>126057948</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550112</v>
+        <v>550202</v>
       </c>
       <c r="R55" t="n">
-        <v>6943293</v>
+        <v>6943212</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6516,7 +6507,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6543,7 +6534,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057948</v>
+        <v>126035217</v>
       </c>
       <c r="B56" t="n">
         <v>92528</v>
@@ -6571,20 +6562,29 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550202</v>
+        <v>550160</v>
       </c>
       <c r="R56" t="n">
-        <v>6943212</v>
+        <v>6943218</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>6 stycken</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -3807,10 +3807,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057942</v>
+        <v>126034784</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,17 +3838,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550179</v>
+        <v>550077</v>
       </c>
       <c r="R29" t="n">
-        <v>6943131</v>
+        <v>6943249</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3878,6 +3878,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav i området</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3904,10 +3909,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126034784</v>
+        <v>126057942</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,17 +3940,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550077</v>
+        <v>550179</v>
       </c>
       <c r="R30" t="n">
-        <v>6943249</v>
+        <v>6943131</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3975,11 +3980,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav i området</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4009,7 +4009,7 @@
         <v>126057925</v>
       </c>
       <c r="B31" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126057387</v>
       </c>
       <c r="B32" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126034466</v>
+        <v>126057943</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4236,17 +4236,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550070</v>
+        <v>550202</v>
       </c>
       <c r="R33" t="n">
-        <v>6943181</v>
+        <v>6943216</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4276,11 +4276,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4310,7 +4305,7 @@
         <v>126034754</v>
       </c>
       <c r="B34" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4418,32 +4413,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126035100</v>
+        <v>126034466</v>
       </c>
       <c r="B35" t="n">
-        <v>80104</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4453,10 +4448,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550152</v>
+        <v>550070</v>
       </c>
       <c r="R35" t="n">
-        <v>6943218</v>
+        <v>6943181</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4489,6 +4484,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,7 +4518,7 @@
         <v>126035073</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,48 +4617,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057943</v>
+        <v>126035100</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>80108</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550202</v>
+        <v>550152</v>
       </c>
       <c r="R37" t="n">
-        <v>6943216</v>
+        <v>6943218</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034913</v>
+        <v>126034773</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,34 +4725,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550089</v>
+        <v>550077</v>
       </c>
       <c r="R38" t="n">
-        <v>6943257</v>
+        <v>6943249</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,7 +4794,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4816,10 +4821,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034773</v>
+        <v>126057394</v>
       </c>
       <c r="B39" t="n">
-        <v>57652</v>
+        <v>78735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4827,29 +4832,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
@@ -4859,10 +4859,10 @@
         <v>550077</v>
       </c>
       <c r="R39" t="n">
-        <v>6943249</v>
+        <v>6943175</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4892,11 +4892,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,10 +4918,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057394</v>
+        <v>126034913</v>
       </c>
       <c r="B40" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,21 +4929,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4958,13 +4953,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550077</v>
+        <v>550089</v>
       </c>
       <c r="R40" t="n">
-        <v>6943175</v>
+        <v>6943257</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4994,6 +4989,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5023,7 +5023,7 @@
         <v>126057405</v>
       </c>
       <c r="B41" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>126057391</v>
       </c>
       <c r="B42" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>126057381</v>
       </c>
       <c r="B43" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057933</v>
+        <v>126033807</v>
       </c>
       <c r="B44" t="n">
-        <v>91256</v>
+        <v>57656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5332,37 +5332,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550185</v>
+        <v>550023</v>
       </c>
       <c r="R44" t="n">
-        <v>6943280</v>
+        <v>6943027</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5392,6 +5397,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,10 +5428,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126033807</v>
+        <v>126057933</v>
       </c>
       <c r="B45" t="n">
-        <v>57652</v>
+        <v>91260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5429,42 +5439,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550023</v>
+        <v>550185</v>
       </c>
       <c r="R45" t="n">
-        <v>6943027</v>
+        <v>6943280</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5494,11 +5499,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5528,7 +5528,7 @@
         <v>126057386</v>
       </c>
       <c r="B46" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5622,45 +5622,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057941</v>
+        <v>126057395</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550157</v>
+        <v>550130</v>
       </c>
       <c r="R47" t="n">
-        <v>6943042</v>
+        <v>6943287</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5693,6 +5693,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5719,45 +5724,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057395</v>
+        <v>126057941</v>
       </c>
       <c r="B48" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550130</v>
+        <v>550157</v>
       </c>
       <c r="R48" t="n">
-        <v>6943287</v>
+        <v>6943042</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5790,11 +5795,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5821,38 +5821,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126033819</v>
+        <v>126033952</v>
       </c>
       <c r="B49" t="n">
-        <v>57652</v>
+        <v>92532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5901,7 +5905,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5928,42 +5932,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126033952</v>
+        <v>126033819</v>
       </c>
       <c r="B50" t="n">
-        <v>92528</v>
+        <v>57656</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6042,7 +6042,7 @@
         <v>126057392</v>
       </c>
       <c r="B51" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6136,48 +6136,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126033968</v>
+        <v>126057901</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>80108</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550004</v>
+        <v>550208</v>
       </c>
       <c r="R52" t="n">
-        <v>6943033</v>
+        <v>6943249</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6233,48 +6233,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057901</v>
+        <v>126033968</v>
       </c>
       <c r="B53" t="n">
-        <v>80104</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550208</v>
+        <v>550004</v>
       </c>
       <c r="R53" t="n">
-        <v>6943249</v>
+        <v>6943033</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6330,48 +6330,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057398</v>
+        <v>126035217</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>92532</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550112</v>
+        <v>550160</v>
       </c>
       <c r="R54" t="n">
-        <v>6943293</v>
+        <v>6943218</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6405,7 +6414,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6432,45 +6441,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057948</v>
+        <v>126057398</v>
       </c>
       <c r="B55" t="n">
-        <v>92528</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550202</v>
+        <v>550112</v>
       </c>
       <c r="R55" t="n">
-        <v>6943212</v>
+        <v>6943293</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6507,7 +6516,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>6 stycken</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6534,10 +6543,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126035217</v>
+        <v>126057948</v>
       </c>
       <c r="B56" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6562,29 +6571,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550160</v>
+        <v>550202</v>
       </c>
       <c r="R56" t="n">
-        <v>6943218</v>
+        <v>6943212</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6648,7 +6648,7 @@
         <v>126034055</v>
       </c>
       <c r="B57" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>126034945</v>
       </c>
       <c r="B58" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>126057400</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>126034470</v>
       </c>
       <c r="B60" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>126035265</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>126035140</v>
       </c>
       <c r="B62" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>126057383</v>
       </c>
       <c r="B63" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>126035020</v>
       </c>
       <c r="B64" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>126057949</v>
       </c>
       <c r="B65" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>126057399</v>
       </c>
       <c r="B66" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>126057397</v>
       </c>
       <c r="B67" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7764,32 +7764,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057380</v>
+        <v>126057404</v>
       </c>
       <c r="B68" t="n">
-        <v>57652</v>
+        <v>92532</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550099</v>
+        <v>550098</v>
       </c>
       <c r="R68" t="n">
-        <v>6943282</v>
+        <v>6943200</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färskt</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7866,10 +7866,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126057404</v>
+        <v>126057403</v>
       </c>
       <c r="B69" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550098</v>
+        <v>550078</v>
       </c>
       <c r="R69" t="n">
-        <v>6943200</v>
+        <v>6943240</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7968,32 +7968,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057403</v>
+        <v>126057380</v>
       </c>
       <c r="B70" t="n">
-        <v>92528</v>
+        <v>57656</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550078</v>
+        <v>550099</v>
       </c>
       <c r="R70" t="n">
-        <v>6943240</v>
+        <v>6943282</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Ringhack på tall. Färskt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8073,7 +8073,7 @@
         <v>126057384</v>
       </c>
       <c r="B71" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>126057389</v>
       </c>
       <c r="B72" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4205,7 +4205,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057943</v>
+        <v>126034466</v>
       </c>
       <c r="B33" t="n">
         <v>78977</v>
@@ -4236,17 +4236,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550202</v>
+        <v>550070</v>
       </c>
       <c r="R33" t="n">
-        <v>6943216</v>
+        <v>6943181</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4276,6 +4276,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,54 +4307,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126034754</v>
+        <v>126035073</v>
       </c>
       <c r="B34" t="n">
-        <v>92532</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550066</v>
+        <v>550142</v>
       </c>
       <c r="R34" t="n">
-        <v>6943216</v>
+        <v>6943223</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4386,7 +4382,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4413,45 +4409,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126034466</v>
+        <v>126034754</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550070</v>
+        <v>550066</v>
       </c>
       <c r="R35" t="n">
-        <v>6943181</v>
+        <v>6943216</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,7 +4493,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,32 +4520,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126035073</v>
+        <v>126035100</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>80108</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4550,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550142</v>
+        <v>550152</v>
       </c>
       <c r="R36" t="n">
-        <v>6943223</v>
+        <v>6943218</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,11 +4591,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,48 +4617,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126035100</v>
+        <v>126057943</v>
       </c>
       <c r="B37" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550152</v>
+        <v>550202</v>
       </c>
       <c r="R37" t="n">
-        <v>6943218</v>
+        <v>6943216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5622,45 +5622,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057395</v>
+        <v>126057941</v>
       </c>
       <c r="B47" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550130</v>
+        <v>550157</v>
       </c>
       <c r="R47" t="n">
-        <v>6943287</v>
+        <v>6943042</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5693,11 +5693,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>120 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5724,45 +5719,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057941</v>
+        <v>126057395</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>98349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550157</v>
+        <v>550130</v>
       </c>
       <c r="R48" t="n">
-        <v>6943042</v>
+        <v>6943287</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5795,6 +5790,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5821,42 +5821,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126033952</v>
+        <v>126033819</v>
       </c>
       <c r="B49" t="n">
-        <v>92532</v>
+        <v>57656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5905,7 +5901,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5932,10 +5928,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126033819</v>
+        <v>126057392</v>
       </c>
       <c r="B50" t="n">
-        <v>57656</v>
+        <v>80080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5943,42 +5939,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R50" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6008,11 +5999,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6039,48 +6025,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126057392</v>
+        <v>126033952</v>
       </c>
       <c r="B51" t="n">
-        <v>80080</v>
+        <v>92532</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R51" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6110,6 +6105,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6136,48 +6136,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126057901</v>
+        <v>126033968</v>
       </c>
       <c r="B52" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550208</v>
+        <v>550004</v>
       </c>
       <c r="R52" t="n">
-        <v>6943249</v>
+        <v>6943033</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6233,45 +6233,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126033968</v>
+        <v>126035217</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550004</v>
+        <v>550160</v>
       </c>
       <c r="R53" t="n">
-        <v>6943033</v>
+        <v>6943218</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,6 +6313,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6330,10 +6344,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126035217</v>
+        <v>126057901</v>
       </c>
       <c r="B54" t="n">
-        <v>92532</v>
+        <v>80108</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6341,46 +6355,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550160</v>
+        <v>550208</v>
       </c>
       <c r="R54" t="n">
-        <v>6943218</v>
+        <v>6943249</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6410,11 +6415,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4009,7 +4009,7 @@
         <v>126057925</v>
       </c>
       <c r="B31" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126057387</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126035073</v>
+        <v>126035100</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>80108</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550142</v>
+        <v>550152</v>
       </c>
       <c r="R34" t="n">
-        <v>6943223</v>
+        <v>6943218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4378,11 +4378,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4409,54 +4404,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126034754</v>
+        <v>126035073</v>
       </c>
       <c r="B35" t="n">
-        <v>92532</v>
+        <v>80080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550066</v>
+        <v>550142</v>
       </c>
       <c r="R35" t="n">
-        <v>6943216</v>
+        <v>6943223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4493,7 +4479,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4520,10 +4506,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126035100</v>
+        <v>126034754</v>
       </c>
       <c r="B36" t="n">
-        <v>80108</v>
+        <v>92532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4531,34 +4517,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550152</v>
+        <v>550066</v>
       </c>
       <c r="R36" t="n">
-        <v>6943218</v>
+        <v>6943216</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4591,6 +4586,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4821,10 +4821,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057394</v>
+        <v>126034913</v>
       </c>
       <c r="B39" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4832,21 +4832,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550077</v>
+        <v>550089</v>
       </c>
       <c r="R39" t="n">
-        <v>6943175</v>
+        <v>6943257</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4892,6 +4892,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4918,10 +4923,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126034913</v>
+        <v>126057391</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4929,21 +4934,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4953,13 +4958,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550089</v>
+        <v>550083</v>
       </c>
       <c r="R40" t="n">
-        <v>6943257</v>
+        <v>6943127</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4989,11 +4994,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057391</v>
+        <v>126057394</v>
       </c>
       <c r="B42" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,21 +5133,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550083</v>
+        <v>550077</v>
       </c>
       <c r="R42" t="n">
-        <v>6943127</v>
+        <v>6943175</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5321,10 +5321,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126033807</v>
+        <v>126057933</v>
       </c>
       <c r="B44" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5332,42 +5332,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550023</v>
+        <v>550185</v>
       </c>
       <c r="R44" t="n">
-        <v>6943027</v>
+        <v>6943280</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,11 +5392,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,10 +5418,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057933</v>
+        <v>126033807</v>
       </c>
       <c r="B45" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5439,37 +5429,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550185</v>
+        <v>550023</v>
       </c>
       <c r="R45" t="n">
-        <v>6943280</v>
+        <v>6943027</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5499,6 +5494,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5525,45 +5525,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057386</v>
+        <v>126057941</v>
       </c>
       <c r="B46" t="n">
-        <v>80109</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550139</v>
+        <v>550157</v>
       </c>
       <c r="R46" t="n">
-        <v>6943330</v>
+        <v>6943042</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5622,45 +5622,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057941</v>
+        <v>126057386</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550157</v>
+        <v>550139</v>
       </c>
       <c r="R47" t="n">
-        <v>6943042</v>
+        <v>6943330</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5722,7 +5722,7 @@
         <v>126057395</v>
       </c>
       <c r="B48" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5928,48 +5928,57 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126057392</v>
+        <v>126033952</v>
       </c>
       <c r="B50" t="n">
-        <v>80080</v>
+        <v>92532</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R50" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5999,6 +6008,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6025,57 +6039,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126033952</v>
+        <v>126057392</v>
       </c>
       <c r="B51" t="n">
-        <v>92532</v>
+        <v>80080</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R51" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6105,11 +6110,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6136,48 +6136,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126033968</v>
+        <v>126057948</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550004</v>
+        <v>550202</v>
       </c>
       <c r="R52" t="n">
-        <v>6943033</v>
+        <v>6943212</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6207,6 +6207,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6233,10 +6238,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126035217</v>
+        <v>126057901</v>
       </c>
       <c r="B53" t="n">
-        <v>92532</v>
+        <v>80108</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6244,46 +6249,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550160</v>
+        <v>550208</v>
       </c>
       <c r="R53" t="n">
-        <v>6943218</v>
+        <v>6943249</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6313,11 +6309,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6344,45 +6335,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057901</v>
+        <v>126057398</v>
       </c>
       <c r="B54" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550208</v>
+        <v>550112</v>
       </c>
       <c r="R54" t="n">
-        <v>6943249</v>
+        <v>6943293</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6415,6 +6406,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6441,7 +6437,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057398</v>
+        <v>126033968</v>
       </c>
       <c r="B55" t="n">
         <v>78977</v>
@@ -6476,13 +6472,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550112</v>
+        <v>550004</v>
       </c>
       <c r="R55" t="n">
-        <v>6943293</v>
+        <v>6943033</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6512,11 +6508,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6543,7 +6534,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057948</v>
+        <v>126035217</v>
       </c>
       <c r="B56" t="n">
         <v>92532</v>
@@ -6571,20 +6562,29 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550202</v>
+        <v>550160</v>
       </c>
       <c r="R56" t="n">
-        <v>6943212</v>
+        <v>6943218</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>6 stycken</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,7 +6645,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034055</v>
+        <v>126034945</v>
       </c>
       <c r="B57" t="n">
         <v>92532</v>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550049</v>
+        <v>550105</v>
       </c>
       <c r="R57" t="n">
-        <v>6943143</v>
+        <v>6943253</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6725,11 +6725,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6756,7 +6751,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034945</v>
+        <v>126034055</v>
       </c>
       <c r="B58" t="n">
         <v>92532</v>
@@ -6800,10 +6795,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550105</v>
+        <v>550049</v>
       </c>
       <c r="R58" t="n">
-        <v>6943253</v>
+        <v>6943143</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6836,6 +6831,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7665,7 +7665,7 @@
         <v>126057397</v>
       </c>
       <c r="B67" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7764,32 +7764,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057404</v>
+        <v>126057380</v>
       </c>
       <c r="B68" t="n">
-        <v>92532</v>
+        <v>57656</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550098</v>
+        <v>550099</v>
       </c>
       <c r="R68" t="n">
-        <v>6943200</v>
+        <v>6943282</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>Ringhack på tall. Färskt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7866,7 +7866,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126057403</v>
+        <v>126057404</v>
       </c>
       <c r="B69" t="n">
         <v>92532</v>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550078</v>
+        <v>550098</v>
       </c>
       <c r="R69" t="n">
-        <v>6943240</v>
+        <v>6943200</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7968,32 +7968,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057380</v>
+        <v>126057403</v>
       </c>
       <c r="B70" t="n">
-        <v>57656</v>
+        <v>92532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550099</v>
+        <v>550078</v>
       </c>
       <c r="R70" t="n">
-        <v>6943282</v>
+        <v>6943240</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färskt</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8070,10 +8070,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126057384</v>
+        <v>126057389</v>
       </c>
       <c r="B71" t="n">
-        <v>57656</v>
+        <v>78736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8081,21 +8081,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550026</v>
+        <v>550212</v>
       </c>
       <c r="R71" t="n">
-        <v>6943025</v>
+        <v>6943141</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8141,11 +8141,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8172,10 +8167,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126057389</v>
+        <v>126057384</v>
       </c>
       <c r="B72" t="n">
-        <v>78736</v>
+        <v>57656</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8183,21 +8178,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8207,10 +8202,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550212</v>
+        <v>550026</v>
       </c>
       <c r="R72" t="n">
-        <v>6943141</v>
+        <v>6943025</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8243,6 +8238,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4923,32 +4923,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057391</v>
+        <v>126057405</v>
       </c>
       <c r="B40" t="n">
-        <v>78736</v>
+        <v>92532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550083</v>
+        <v>550073</v>
       </c>
       <c r="R40" t="n">
-        <v>6943127</v>
+        <v>6943181</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4994,6 +4994,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5020,32 +5025,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057405</v>
+        <v>126057394</v>
       </c>
       <c r="B41" t="n">
-        <v>92532</v>
+        <v>78735</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5055,10 +5060,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550073</v>
+        <v>550077</v>
       </c>
       <c r="R41" t="n">
-        <v>6943181</v>
+        <v>6943175</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5091,11 +5096,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057394</v>
+        <v>126057391</v>
       </c>
       <c r="B42" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,21 +5133,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550077</v>
+        <v>550083</v>
       </c>
       <c r="R42" t="n">
-        <v>6943175</v>
+        <v>6943127</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5821,38 +5821,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126033819</v>
+        <v>126033952</v>
       </c>
       <c r="B49" t="n">
-        <v>57656</v>
+        <v>92532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5901,7 +5905,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5928,57 +5932,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126033952</v>
+        <v>126057392</v>
       </c>
       <c r="B50" t="n">
-        <v>92532</v>
+        <v>80080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R50" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6008,11 +6003,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6039,10 +6029,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126057392</v>
+        <v>126033819</v>
       </c>
       <c r="B51" t="n">
-        <v>80080</v>
+        <v>57656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6050,37 +6040,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R51" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6110,6 +6105,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126035265</v>
+        <v>126057383</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550162</v>
+        <v>550081</v>
       </c>
       <c r="R61" t="n">
-        <v>6943239</v>
+        <v>6943139</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7127,6 +7127,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7153,10 +7158,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126035140</v>
+        <v>126035265</v>
       </c>
       <c r="B62" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7164,21 +7169,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7188,10 +7193,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550152</v>
+        <v>550162</v>
       </c>
       <c r="R62" t="n">
-        <v>6943218</v>
+        <v>6943239</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7224,11 +7229,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7255,10 +7255,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057383</v>
+        <v>126035140</v>
       </c>
       <c r="B63" t="n">
-        <v>57656</v>
+        <v>80080</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550081</v>
+        <v>550152</v>
       </c>
       <c r="R63" t="n">
-        <v>6943139</v>
+        <v>6943218</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Äldre spår</t>
+          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7764,32 +7764,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057380</v>
+        <v>126057404</v>
       </c>
       <c r="B68" t="n">
-        <v>57656</v>
+        <v>92532</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550099</v>
+        <v>550098</v>
       </c>
       <c r="R68" t="n">
-        <v>6943282</v>
+        <v>6943200</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färskt</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7866,7 +7866,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126057404</v>
+        <v>126057403</v>
       </c>
       <c r="B69" t="n">
         <v>92532</v>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550098</v>
+        <v>550078</v>
       </c>
       <c r="R69" t="n">
-        <v>6943200</v>
+        <v>6943240</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7968,32 +7968,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057403</v>
+        <v>126057380</v>
       </c>
       <c r="B70" t="n">
-        <v>92532</v>
+        <v>57656</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550078</v>
+        <v>550099</v>
       </c>
       <c r="R70" t="n">
-        <v>6943240</v>
+        <v>6943282</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Ringhack på tall. Färskt</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4006,45 +4006,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057925</v>
+        <v>126057387</v>
       </c>
       <c r="B31" t="n">
-        <v>98352</v>
+        <v>98373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550203</v>
+        <v>550127</v>
       </c>
       <c r="R31" t="n">
-        <v>6943259</v>
+        <v>6943306</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4077,11 +4077,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4108,45 +4103,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057387</v>
+        <v>126057925</v>
       </c>
       <c r="B32" t="n">
-        <v>98373</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550127</v>
+        <v>550203</v>
       </c>
       <c r="R32" t="n">
-        <v>6943306</v>
+        <v>6943259</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4179,6 +4174,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4307,10 +4307,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126035100</v>
+        <v>126034754</v>
       </c>
       <c r="B34" t="n">
-        <v>80108</v>
+        <v>92532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,34 +4318,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550152</v>
+        <v>550066</v>
       </c>
       <c r="R34" t="n">
-        <v>6943218</v>
+        <v>6943216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4378,6 +4387,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,32 +4418,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126035073</v>
+        <v>126035100</v>
       </c>
       <c r="B35" t="n">
-        <v>80080</v>
+        <v>80108</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4439,10 +4453,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550142</v>
+        <v>550152</v>
       </c>
       <c r="R35" t="n">
-        <v>6943223</v>
+        <v>6943218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,11 +4489,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4506,54 +4515,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034754</v>
+        <v>126035073</v>
       </c>
       <c r="B36" t="n">
-        <v>92532</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550066</v>
+        <v>550142</v>
       </c>
       <c r="R36" t="n">
-        <v>6943216</v>
+        <v>6943223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034773</v>
+        <v>126034913</v>
       </c>
       <c r="B38" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,39 +4725,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550077</v>
+        <v>550089</v>
       </c>
       <c r="R38" t="n">
-        <v>6943249</v>
+        <v>6943257</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4794,7 +4789,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4821,10 +4816,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034913</v>
+        <v>126057394</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4832,21 +4827,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4856,13 +4851,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550089</v>
+        <v>550077</v>
       </c>
       <c r="R39" t="n">
-        <v>6943257</v>
+        <v>6943175</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4892,11 +4887,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,32 +4913,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057405</v>
+        <v>126057391</v>
       </c>
       <c r="B40" t="n">
-        <v>92532</v>
+        <v>78736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4958,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550073</v>
+        <v>550083</v>
       </c>
       <c r="R40" t="n">
-        <v>6943181</v>
+        <v>6943127</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4994,11 +4984,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5025,10 +5010,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057394</v>
+        <v>126034773</v>
       </c>
       <c r="B41" t="n">
-        <v>78735</v>
+        <v>57656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5036,24 +5021,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
@@ -5063,10 +5053,10 @@
         <v>550077</v>
       </c>
       <c r="R41" t="n">
-        <v>6943175</v>
+        <v>6943249</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5096,6 +5086,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5122,32 +5117,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057391</v>
+        <v>126057405</v>
       </c>
       <c r="B42" t="n">
-        <v>78736</v>
+        <v>92532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5157,10 +5152,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550083</v>
+        <v>550073</v>
       </c>
       <c r="R42" t="n">
-        <v>6943127</v>
+        <v>6943181</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5193,6 +5188,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5525,45 +5525,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057941</v>
+        <v>126057386</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550157</v>
+        <v>550139</v>
       </c>
       <c r="R46" t="n">
-        <v>6943042</v>
+        <v>6943330</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5622,45 +5622,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057386</v>
+        <v>126057941</v>
       </c>
       <c r="B47" t="n">
-        <v>80109</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550139</v>
+        <v>550157</v>
       </c>
       <c r="R47" t="n">
-        <v>6943330</v>
+        <v>6943042</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6136,48 +6136,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126057948</v>
+        <v>126033968</v>
       </c>
       <c r="B52" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550202</v>
+        <v>550004</v>
       </c>
       <c r="R52" t="n">
-        <v>6943212</v>
+        <v>6943033</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6207,11 +6207,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6238,10 +6233,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057901</v>
+        <v>126035217</v>
       </c>
       <c r="B53" t="n">
-        <v>80108</v>
+        <v>92532</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6249,37 +6244,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550208</v>
+        <v>550160</v>
       </c>
       <c r="R53" t="n">
-        <v>6943249</v>
+        <v>6943218</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6309,6 +6313,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6335,45 +6344,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057398</v>
+        <v>126057901</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>80108</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550112</v>
+        <v>550208</v>
       </c>
       <c r="R54" t="n">
-        <v>6943293</v>
+        <v>6943249</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6406,11 +6415,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6437,7 +6441,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126033968</v>
+        <v>126057398</v>
       </c>
       <c r="B55" t="n">
         <v>78977</v>
@@ -6472,13 +6476,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550004</v>
+        <v>550112</v>
       </c>
       <c r="R55" t="n">
-        <v>6943033</v>
+        <v>6943293</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6508,6 +6512,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6534,7 +6543,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126035217</v>
+        <v>126057948</v>
       </c>
       <c r="B56" t="n">
         <v>92532</v>
@@ -6562,29 +6571,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550160</v>
+        <v>550202</v>
       </c>
       <c r="R56" t="n">
-        <v>6943218</v>
+        <v>6943212</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6645,7 +6645,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034945</v>
+        <v>126034055</v>
       </c>
       <c r="B57" t="n">
         <v>92532</v>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550105</v>
+        <v>550049</v>
       </c>
       <c r="R57" t="n">
-        <v>6943253</v>
+        <v>6943143</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6725,6 +6725,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6751,7 +6756,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034055</v>
+        <v>126034945</v>
       </c>
       <c r="B58" t="n">
         <v>92532</v>
@@ -6795,10 +6800,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550049</v>
+        <v>550105</v>
       </c>
       <c r="R58" t="n">
-        <v>6943143</v>
+        <v>6943253</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6831,11 +6836,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057383</v>
+        <v>126035265</v>
       </c>
       <c r="B61" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550081</v>
+        <v>550162</v>
       </c>
       <c r="R61" t="n">
-        <v>6943139</v>
+        <v>6943239</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7127,11 +7127,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7158,10 +7153,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126035265</v>
+        <v>126035140</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7169,21 +7164,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7193,10 +7188,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550162</v>
+        <v>550152</v>
       </c>
       <c r="R62" t="n">
-        <v>6943239</v>
+        <v>6943218</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7229,6 +7224,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7255,10 +7255,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126035140</v>
+        <v>126057383</v>
       </c>
       <c r="B63" t="n">
-        <v>80080</v>
+        <v>57656</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550152</v>
+        <v>550081</v>
       </c>
       <c r="R63" t="n">
-        <v>6943218</v>
+        <v>6943139</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7764,7 +7764,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057404</v>
+        <v>126057403</v>
       </c>
       <c r="B68" t="n">
         <v>92532</v>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550098</v>
+        <v>550078</v>
       </c>
       <c r="R68" t="n">
-        <v>6943200</v>
+        <v>6943240</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7866,7 +7866,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126057403</v>
+        <v>126057404</v>
       </c>
       <c r="B69" t="n">
         <v>92532</v>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550078</v>
+        <v>550098</v>
       </c>
       <c r="R69" t="n">
-        <v>6943240</v>
+        <v>6943200</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8070,10 +8070,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126057389</v>
+        <v>126057384</v>
       </c>
       <c r="B71" t="n">
-        <v>78736</v>
+        <v>57656</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8081,21 +8081,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550212</v>
+        <v>550026</v>
       </c>
       <c r="R71" t="n">
-        <v>6943141</v>
+        <v>6943025</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8141,6 +8141,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8167,10 +8172,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126057384</v>
+        <v>126057389</v>
       </c>
       <c r="B72" t="n">
-        <v>57656</v>
+        <v>78736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8178,21 +8183,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8202,10 +8207,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550026</v>
+        <v>550212</v>
       </c>
       <c r="R72" t="n">
-        <v>6943025</v>
+        <v>6943141</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8238,11 +8243,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4205,7 +4205,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126034466</v>
+        <v>126057943</v>
       </c>
       <c r="B33" t="n">
         <v>78977</v>
@@ -4236,17 +4236,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550070</v>
+        <v>550202</v>
       </c>
       <c r="R33" t="n">
-        <v>6943181</v>
+        <v>6943216</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4276,11 +4276,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4307,54 +4302,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126034754</v>
+        <v>126034466</v>
       </c>
       <c r="B34" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550066</v>
+        <v>550070</v>
       </c>
       <c r="R34" t="n">
-        <v>6943216</v>
+        <v>6943181</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4391,7 +4377,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,10 +4404,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126035100</v>
+        <v>126034754</v>
       </c>
       <c r="B35" t="n">
-        <v>80108</v>
+        <v>92532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,34 +4415,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550152</v>
+        <v>550066</v>
       </c>
       <c r="R35" t="n">
-        <v>6943218</v>
+        <v>6943216</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4489,6 +4484,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,32 +4515,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126035073</v>
+        <v>126035100</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>80108</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550142</v>
+        <v>550152</v>
       </c>
       <c r="R36" t="n">
-        <v>6943223</v>
+        <v>6943218</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,11 +4586,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,10 +4612,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057943</v>
+        <v>126035073</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4628,37 +4623,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550202</v>
+        <v>550142</v>
       </c>
       <c r="R37" t="n">
-        <v>6943216</v>
+        <v>6943223</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4688,6 +4683,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5321,10 +5321,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057933</v>
+        <v>126033807</v>
       </c>
       <c r="B44" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5332,37 +5332,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550185</v>
+        <v>550023</v>
       </c>
       <c r="R44" t="n">
-        <v>6943280</v>
+        <v>6943027</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5392,6 +5397,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,10 +5428,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126033807</v>
+        <v>126057933</v>
       </c>
       <c r="B45" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5429,42 +5439,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550023</v>
+        <v>550185</v>
       </c>
       <c r="R45" t="n">
-        <v>6943027</v>
+        <v>6943280</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5494,11 +5499,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6645,57 +6645,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034055</v>
+        <v>126057400</v>
       </c>
       <c r="B57" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550049</v>
+        <v>550058</v>
       </c>
       <c r="R57" t="n">
-        <v>6943143</v>
+        <v>6943054</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6725,11 +6716,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6756,7 +6742,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034945</v>
+        <v>126034055</v>
       </c>
       <c r="B58" t="n">
         <v>92532</v>
@@ -6800,10 +6786,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550105</v>
+        <v>550049</v>
       </c>
       <c r="R58" t="n">
-        <v>6943253</v>
+        <v>6943143</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6836,6 +6822,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6862,48 +6853,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126057400</v>
+        <v>126034945</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550058</v>
+        <v>550105</v>
       </c>
       <c r="R59" t="n">
-        <v>6943054</v>
+        <v>6943253</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -3810,7 +3810,7 @@
         <v>126034784</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>126057942</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4006,45 +4006,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057387</v>
+        <v>126057925</v>
       </c>
       <c r="B31" t="n">
-        <v>98373</v>
+        <v>98361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550127</v>
+        <v>550203</v>
       </c>
       <c r="R31" t="n">
-        <v>6943306</v>
+        <v>6943259</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4077,6 +4077,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4103,45 +4108,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057925</v>
+        <v>126057387</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>98382</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550203</v>
+        <v>550127</v>
       </c>
       <c r="R32" t="n">
-        <v>6943259</v>
+        <v>6943306</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4174,11 +4179,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4205,48 +4205,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057943</v>
+        <v>126034754</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>92535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550202</v>
+        <v>550066</v>
       </c>
       <c r="R33" t="n">
         <v>6943216</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4276,6 +4285,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4305,7 +4319,7 @@
         <v>126034466</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4404,10 +4418,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126034754</v>
+        <v>126035100</v>
       </c>
       <c r="B35" t="n">
-        <v>92532</v>
+        <v>80111</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,43 +4429,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550066</v>
+        <v>550152</v>
       </c>
       <c r="R35" t="n">
-        <v>6943216</v>
+        <v>6943218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4484,11 +4489,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,32 +4515,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126035100</v>
+        <v>126035073</v>
       </c>
       <c r="B36" t="n">
-        <v>80108</v>
+        <v>80083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550152</v>
+        <v>550142</v>
       </c>
       <c r="R36" t="n">
-        <v>6943218</v>
+        <v>6943223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,6 +4586,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4612,10 +4617,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126035073</v>
+        <v>126057943</v>
       </c>
       <c r="B37" t="n">
-        <v>80080</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4623,37 +4628,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550142</v>
+        <v>550202</v>
       </c>
       <c r="R37" t="n">
-        <v>6943223</v>
+        <v>6943216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4683,11 +4688,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034913</v>
+        <v>126034773</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,34 +4725,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550089</v>
+        <v>550077</v>
       </c>
       <c r="R38" t="n">
-        <v>6943257</v>
+        <v>6943249</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,7 +4794,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,7 +4824,7 @@
         <v>126057394</v>
       </c>
       <c r="B39" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4913,32 +4918,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057391</v>
+        <v>126057405</v>
       </c>
       <c r="B40" t="n">
-        <v>78736</v>
+        <v>92535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4948,10 +4953,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550083</v>
+        <v>550073</v>
       </c>
       <c r="R40" t="n">
-        <v>6943127</v>
+        <v>6943181</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4984,6 +4989,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5010,10 +5020,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126034773</v>
+        <v>126034913</v>
       </c>
       <c r="B41" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5021,39 +5031,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550077</v>
+        <v>550089</v>
       </c>
       <c r="R41" t="n">
-        <v>6943249</v>
+        <v>6943257</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5090,7 +5095,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5117,32 +5122,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057405</v>
+        <v>126057391</v>
       </c>
       <c r="B42" t="n">
-        <v>92532</v>
+        <v>78739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550073</v>
+        <v>550083</v>
       </c>
       <c r="R42" t="n">
-        <v>6943181</v>
+        <v>6943127</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5188,11 +5193,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,7 +5222,7 @@
         <v>126057381</v>
       </c>
       <c r="B43" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>126033807</v>
       </c>
       <c r="B44" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>126057933</v>
       </c>
       <c r="B45" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>126057386</v>
       </c>
       <c r="B46" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>126057941</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>126057395</v>
       </c>
       <c r="B48" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>126033952</v>
       </c>
       <c r="B49" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5932,10 +5932,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126057392</v>
+        <v>126033819</v>
       </c>
       <c r="B50" t="n">
-        <v>80080</v>
+        <v>57657</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5943,37 +5943,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550121</v>
+        <v>550004</v>
       </c>
       <c r="R50" t="n">
-        <v>6943289</v>
+        <v>6943033</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6003,6 +6008,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6029,10 +6039,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126033819</v>
+        <v>126057392</v>
       </c>
       <c r="B51" t="n">
-        <v>57656</v>
+        <v>80083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6040,42 +6050,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550004</v>
+        <v>550121</v>
       </c>
       <c r="R51" t="n">
-        <v>6943033</v>
+        <v>6943289</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6105,11 +6110,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6139,7 +6139,7 @@
         <v>126033968</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>126035217</v>
       </c>
       <c r="B53" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>126057901</v>
       </c>
       <c r="B54" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>126057398</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>126057948</v>
       </c>
       <c r="B56" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6645,48 +6645,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126057400</v>
+        <v>126034055</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>92535</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550058</v>
+        <v>550049</v>
       </c>
       <c r="R57" t="n">
-        <v>6943054</v>
+        <v>6943143</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6716,6 +6725,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6742,10 +6756,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034055</v>
+        <v>126034945</v>
       </c>
       <c r="B58" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6786,10 +6800,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550049</v>
+        <v>550105</v>
       </c>
       <c r="R58" t="n">
-        <v>6943143</v>
+        <v>6943253</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6822,11 +6836,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av svampen i områet</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6853,57 +6862,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126034945</v>
+        <v>126057400</v>
       </c>
       <c r="B59" t="n">
-        <v>92532</v>
+        <v>78980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550105</v>
+        <v>550058</v>
       </c>
       <c r="R59" t="n">
-        <v>6943253</v>
+        <v>6943054</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>126034470</v>
       </c>
       <c r="B60" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126035265</v>
+        <v>126057383</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550162</v>
+        <v>550081</v>
       </c>
       <c r="R61" t="n">
-        <v>6943239</v>
+        <v>6943139</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7127,6 +7127,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7153,10 +7158,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126035140</v>
+        <v>126035265</v>
       </c>
       <c r="B62" t="n">
-        <v>80080</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7164,21 +7169,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7188,10 +7193,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550152</v>
+        <v>550162</v>
       </c>
       <c r="R62" t="n">
-        <v>6943218</v>
+        <v>6943239</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7224,11 +7229,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7255,10 +7255,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057383</v>
+        <v>126035140</v>
       </c>
       <c r="B63" t="n">
-        <v>57656</v>
+        <v>80083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550081</v>
+        <v>550152</v>
       </c>
       <c r="R63" t="n">
-        <v>6943139</v>
+        <v>6943218</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Äldre spår</t>
+          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7360,7 +7360,7 @@
         <v>126035020</v>
       </c>
       <c r="B64" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>126057949</v>
       </c>
       <c r="B65" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>126057399</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>126057397</v>
       </c>
       <c r="B67" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7764,32 +7764,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057403</v>
+        <v>126057380</v>
       </c>
       <c r="B68" t="n">
-        <v>92532</v>
+        <v>57657</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550078</v>
+        <v>550099</v>
       </c>
       <c r="R68" t="n">
-        <v>6943240</v>
+        <v>6943282</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Ringhack på tall. Färskt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7869,7 +7869,7 @@
         <v>126057404</v>
       </c>
       <c r="B69" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7968,32 +7968,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057380</v>
+        <v>126057403</v>
       </c>
       <c r="B70" t="n">
-        <v>57656</v>
+        <v>92535</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550099</v>
+        <v>550078</v>
       </c>
       <c r="R70" t="n">
-        <v>6943282</v>
+        <v>6943240</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färskt</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8073,7 +8073,7 @@
         <v>126057384</v>
       </c>
       <c r="B71" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>126057389</v>
       </c>
       <c r="B72" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -3807,7 +3807,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126034784</v>
+        <v>126057942</v>
       </c>
       <c r="B29" t="n">
         <v>78980</v>
@@ -3838,17 +3838,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550077</v>
+        <v>550179</v>
       </c>
       <c r="R29" t="n">
-        <v>6943249</v>
+        <v>6943131</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3878,11 +3878,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav i området</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3909,7 +3904,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057942</v>
+        <v>126034784</v>
       </c>
       <c r="B30" t="n">
         <v>78980</v>
@@ -3940,17 +3935,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550179</v>
+        <v>550077</v>
       </c>
       <c r="R30" t="n">
-        <v>6943131</v>
+        <v>6943249</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3980,6 +3975,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav i området</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4205,57 +4205,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126034754</v>
+        <v>126057943</v>
       </c>
       <c r="B33" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550066</v>
+        <v>550202</v>
       </c>
       <c r="R33" t="n">
         <v>6943216</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4285,11 +4276,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4617,48 +4603,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057943</v>
+        <v>126034754</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550202</v>
+        <v>550066</v>
       </c>
       <c r="R37" t="n">
         <v>6943216</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4688,6 +4683,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034773</v>
+        <v>126034913</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,39 +4725,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550077</v>
+        <v>550089</v>
       </c>
       <c r="R38" t="n">
-        <v>6943249</v>
+        <v>6943257</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4794,7 +4789,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4821,10 +4816,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057394</v>
+        <v>126034773</v>
       </c>
       <c r="B39" t="n">
-        <v>78738</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4832,24 +4827,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
@@ -4859,10 +4859,10 @@
         <v>550077</v>
       </c>
       <c r="R39" t="n">
-        <v>6943175</v>
+        <v>6943249</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4892,6 +4892,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4918,32 +4923,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057405</v>
+        <v>126057394</v>
       </c>
       <c r="B40" t="n">
-        <v>92535</v>
+        <v>78738</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4953,10 +4958,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550073</v>
+        <v>550077</v>
       </c>
       <c r="R40" t="n">
-        <v>6943181</v>
+        <v>6943175</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4989,11 +4994,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5020,32 +5020,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126034913</v>
+        <v>126057405</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550089</v>
+        <v>550073</v>
       </c>
       <c r="R41" t="n">
-        <v>6943257</v>
+        <v>6943181</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -7764,32 +7764,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057380</v>
+        <v>126057404</v>
       </c>
       <c r="B68" t="n">
-        <v>57657</v>
+        <v>92535</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550099</v>
+        <v>550098</v>
       </c>
       <c r="R68" t="n">
-        <v>6943282</v>
+        <v>6943200</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färskt</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7866,7 +7866,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126057404</v>
+        <v>126057403</v>
       </c>
       <c r="B69" t="n">
         <v>92535</v>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550098</v>
+        <v>550078</v>
       </c>
       <c r="R69" t="n">
-        <v>6943200</v>
+        <v>6943240</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7968,32 +7968,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057403</v>
+        <v>126057380</v>
       </c>
       <c r="B70" t="n">
-        <v>92535</v>
+        <v>57657</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550078</v>
+        <v>550099</v>
       </c>
       <c r="R70" t="n">
-        <v>6943240</v>
+        <v>6943282</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Ringhack på tall. Färskt</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -3807,7 +3807,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057942</v>
+        <v>126034784</v>
       </c>
       <c r="B29" t="n">
         <v>78980</v>
@@ -3838,17 +3838,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550179</v>
+        <v>550077</v>
       </c>
       <c r="R29" t="n">
-        <v>6943131</v>
+        <v>6943249</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3878,6 +3878,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav i området</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3904,7 +3909,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126034784</v>
+        <v>126057942</v>
       </c>
       <c r="B30" t="n">
         <v>78980</v>
@@ -3935,17 +3940,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550077</v>
+        <v>550179</v>
       </c>
       <c r="R30" t="n">
-        <v>6943249</v>
+        <v>6943131</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3975,11 +3980,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav i området</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4302,32 +4302,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126034466</v>
+        <v>126035100</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>80111</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550070</v>
+        <v>550152</v>
       </c>
       <c r="R34" t="n">
-        <v>6943181</v>
+        <v>6943218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4373,11 +4373,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,32 +4399,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126035100</v>
+        <v>126035073</v>
       </c>
       <c r="B35" t="n">
-        <v>80111</v>
+        <v>80083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4439,10 +4434,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550152</v>
+        <v>550142</v>
       </c>
       <c r="R35" t="n">
-        <v>6943218</v>
+        <v>6943223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,6 +4470,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4501,10 +4501,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126035073</v>
+        <v>126034466</v>
       </c>
       <c r="B36" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550142</v>
+        <v>550070</v>
       </c>
       <c r="R36" t="n">
-        <v>6943223</v>
+        <v>6943181</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034913</v>
+        <v>126034773</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,34 +4725,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550089</v>
+        <v>550077</v>
       </c>
       <c r="R38" t="n">
-        <v>6943257</v>
+        <v>6943249</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4789,7 +4794,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4816,10 +4821,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034773</v>
+        <v>126034913</v>
       </c>
       <c r="B39" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4827,39 +4832,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550077</v>
+        <v>550089</v>
       </c>
       <c r="R39" t="n">
-        <v>6943249</v>
+        <v>6943257</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>Riklig förekomst av garnlav inom området med stora draperier av garnlav</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6136,48 +6136,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126033968</v>
+        <v>126057901</v>
       </c>
       <c r="B52" t="n">
-        <v>78980</v>
+        <v>80111</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550004</v>
+        <v>550208</v>
       </c>
       <c r="R52" t="n">
-        <v>6943033</v>
+        <v>6943249</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6233,57 +6233,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126035217</v>
+        <v>126057398</v>
       </c>
       <c r="B53" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550160</v>
+        <v>550112</v>
       </c>
       <c r="R53" t="n">
-        <v>6943218</v>
+        <v>6943293</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6317,7 +6308,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6344,48 +6335,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057901</v>
+        <v>126033968</v>
       </c>
       <c r="B54" t="n">
-        <v>80111</v>
+        <v>78980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550208</v>
+        <v>550004</v>
       </c>
       <c r="R54" t="n">
-        <v>6943249</v>
+        <v>6943033</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6441,48 +6432,57 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057398</v>
+        <v>126035217</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550112</v>
+        <v>550160</v>
       </c>
       <c r="R55" t="n">
-        <v>6943293</v>
+        <v>6943218</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057383</v>
+        <v>126035265</v>
       </c>
       <c r="B61" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550081</v>
+        <v>550162</v>
       </c>
       <c r="R61" t="n">
-        <v>6943139</v>
+        <v>6943239</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7127,11 +7127,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7158,10 +7153,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126035265</v>
+        <v>126035140</v>
       </c>
       <c r="B62" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7169,21 +7164,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7193,10 +7188,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550162</v>
+        <v>550152</v>
       </c>
       <c r="R62" t="n">
-        <v>6943239</v>
+        <v>6943218</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7229,6 +7224,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7255,10 +7255,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126035140</v>
+        <v>126057383</v>
       </c>
       <c r="B63" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550152</v>
+        <v>550081</v>
       </c>
       <c r="R63" t="n">
-        <v>6943218</v>
+        <v>6943139</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Lunglav på lövträd som spridit sig till grankvistar i närheten.</t>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4205,48 +4205,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057943</v>
+        <v>126035100</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>80111</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550202</v>
+        <v>550152</v>
       </c>
       <c r="R33" t="n">
-        <v>6943216</v>
+        <v>6943218</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4302,32 +4302,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126035100</v>
+        <v>126035073</v>
       </c>
       <c r="B34" t="n">
-        <v>80111</v>
+        <v>80083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550152</v>
+        <v>550142</v>
       </c>
       <c r="R34" t="n">
-        <v>6943218</v>
+        <v>6943223</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4373,6 +4373,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,10 +4404,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126035073</v>
+        <v>126034466</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4410,21 +4415,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4434,10 +4439,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550142</v>
+        <v>550070</v>
       </c>
       <c r="R35" t="n">
-        <v>6943223</v>
+        <v>6943181</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4474,7 +4479,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4501,45 +4506,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034466</v>
+        <v>126034754</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550070</v>
+        <v>550066</v>
       </c>
       <c r="R36" t="n">
-        <v>6943181</v>
+        <v>6943216</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4576,7 +4590,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4603,57 +4617,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034754</v>
+        <v>126057943</v>
       </c>
       <c r="B37" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550066</v>
+        <v>550202</v>
       </c>
       <c r="R37" t="n">
         <v>6943216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4683,11 +4688,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -8070,10 +8070,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126057384</v>
+        <v>126057389</v>
       </c>
       <c r="B71" t="n">
-        <v>57657</v>
+        <v>78739</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8081,21 +8081,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550026</v>
+        <v>550212</v>
       </c>
       <c r="R71" t="n">
-        <v>6943025</v>
+        <v>6943141</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8141,11 +8141,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8172,10 +8167,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126057389</v>
+        <v>126057384</v>
       </c>
       <c r="B72" t="n">
-        <v>78739</v>
+        <v>57657</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8183,21 +8178,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8207,10 +8202,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550212</v>
+        <v>550026</v>
       </c>
       <c r="R72" t="n">
-        <v>6943141</v>
+        <v>6943025</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8243,6 +8238,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -4205,48 +4205,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126035100</v>
+        <v>126057943</v>
       </c>
       <c r="B33" t="n">
-        <v>80111</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grössjöbäcken, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550152</v>
+        <v>550202</v>
       </c>
       <c r="R33" t="n">
-        <v>6943218</v>
+        <v>6943216</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4302,32 +4302,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126035073</v>
+        <v>126035100</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>80111</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550142</v>
+        <v>550152</v>
       </c>
       <c r="R34" t="n">
-        <v>6943223</v>
+        <v>6943218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4373,11 +4373,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,10 +4399,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126034466</v>
+        <v>126035073</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,21 +4410,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4439,10 +4434,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550070</v>
+        <v>550142</v>
       </c>
       <c r="R35" t="n">
-        <v>6943181</v>
+        <v>6943223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4479,7 +4474,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4506,54 +4501,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034754</v>
+        <v>126034466</v>
       </c>
       <c r="B36" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550066</v>
+        <v>550070</v>
       </c>
       <c r="R36" t="n">
-        <v>6943216</v>
+        <v>6943181</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4576,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,48 +4603,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057943</v>
+        <v>126034754</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Grössjöbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550202</v>
+        <v>550066</v>
       </c>
       <c r="R37" t="n">
         <v>6943216</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4688,6 +4683,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5821,42 +5821,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126033952</v>
+        <v>126033819</v>
       </c>
       <c r="B49" t="n">
-        <v>92535</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5905,7 +5901,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5932,38 +5928,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126033819</v>
+        <v>126033952</v>
       </c>
       <c r="B50" t="n">
-        <v>57657</v>
+        <v>92535</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 23965-2025 artfynd.xlsx
+++ b/artfynd/A 23965-2025 artfynd.xlsx
@@ -5821,38 +5821,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126033819</v>
+        <v>126033952</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>92535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5901,7 +5905,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall färska</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5928,42 +5932,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126033952</v>
+        <v>126033819</v>
       </c>
       <c r="B50" t="n">
-        <v>92535</v>
+        <v>57657</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -8070,10 +8070,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126057389</v>
+        <v>126057384</v>
       </c>
       <c r="B71" t="n">
-        <v>78739</v>
+        <v>57657</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8081,21 +8081,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550212</v>
+        <v>550026</v>
       </c>
       <c r="R71" t="n">
-        <v>6943141</v>
+        <v>6943025</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8141,6 +8141,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8167,10 +8172,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126057384</v>
+        <v>126057389</v>
       </c>
       <c r="B72" t="n">
-        <v>57657</v>
+        <v>78739</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8178,21 +8183,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8202,10 +8207,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550026</v>
+        <v>550212</v>
       </c>
       <c r="R72" t="n">
-        <v>6943025</v>
+        <v>6943141</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8238,11 +8243,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
